--- a/Data/output.xlsx
+++ b/Data/output.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Base mortality income</t>
   </si>
@@ -29,7 +29,22 @@
     <t>Base net cfs</t>
   </si>
   <si>
+    <t>AA Late mortality income</t>
+  </si>
+  <si>
+    <t>AA Late prepayment income</t>
+  </si>
+  <si>
+    <t>AA Late service fee</t>
+  </si>
+  <si>
+    <t>AA Late net cfs</t>
+  </si>
+  <si>
     <t>Base OLB</t>
+  </si>
+  <si>
+    <t>AA Late OLB</t>
   </si>
 </sst>
 </file>
@@ -393,10 +408,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E202"/>
+  <dimension ref="A1:I202"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -409,8 +424,20 @@
       <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="2">
         <v>45657</v>
       </c>
@@ -426,1997 +453,3413 @@
       <c r="E2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="2">
         <v>45747</v>
       </c>
       <c r="B3">
-        <v>10013316.20978686</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>3764971.4558153</v>
+        <v>9151.724421986528</v>
       </c>
       <c r="D3">
-        <v>48690</v>
+        <v>756.8671481683114</v>
       </c>
       <c r="E3">
-        <v>13729597.66560216</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>8394.857273818216</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>1816.513244976703</v>
+      </c>
+      <c r="H3">
+        <v>757.7882450230778</v>
+      </c>
+      <c r="I3">
+        <v>1058.724999953625</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="2">
         <v>45838</v>
       </c>
       <c r="B4">
-        <v>9962894.257646605</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>3746012.980263615</v>
+        <v>9212.597212280683</v>
       </c>
       <c r="D4">
-        <v>121725</v>
+        <v>764.1616119101782</v>
       </c>
       <c r="E4">
-        <v>13587182.23791022</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>8448.435600370507</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>1837.901938990991</v>
+      </c>
+      <c r="H4">
+        <v>767.8742728652062</v>
+      </c>
+      <c r="I4">
+        <v>1070.027666125785</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="2">
         <v>45930</v>
       </c>
       <c r="B5">
-        <v>9912726.204734579</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>3727149.969923144</v>
+        <v>9273.951307613215</v>
       </c>
       <c r="D5">
-        <v>194760</v>
+        <v>771.5482454798276</v>
       </c>
       <c r="E5">
-        <v>13445116.17465772</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>8502.403062133388</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>1859.557797159788</v>
+      </c>
+      <c r="H5">
+        <v>778.1038900473957</v>
+      </c>
+      <c r="I5">
+        <v>1081.453907112392</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="2">
         <v>46022</v>
       </c>
       <c r="B6">
-        <v>9862810.772543788</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>3708381.944079785</v>
+        <v>9335.791177463103</v>
       </c>
       <c r="D6">
-        <v>267795</v>
+        <v>779.0284164243171</v>
       </c>
       <c r="E6">
-        <v>13303397.71662357</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>8556.762761038786</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>1881.484376736772</v>
+      </c>
+      <c r="H6">
+        <v>788.4792637630562</v>
+      </c>
+      <c r="I6">
+        <v>1093.005112973716</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="2">
         <v>46112</v>
       </c>
       <c r="B7">
-        <v>11108749.05790437</v>
+        <v>49000.70978758943</v>
       </c>
       <c r="C7">
-        <v>3684218.173720573</v>
+        <v>9278.483994581486</v>
       </c>
       <c r="D7">
-        <v>340830</v>
+        <v>779.367181422806</v>
       </c>
       <c r="E7">
-        <v>14452137.23162494</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>57499.8266007481</v>
+      </c>
+      <c r="F7">
+        <v>13239.41039301298</v>
+      </c>
+      <c r="G7">
+        <v>1899.568394143585</v>
+      </c>
+      <c r="H7">
+        <v>797.5317498079805</v>
+      </c>
+      <c r="I7">
+        <v>14341.44703734859</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="2">
         <v>46203</v>
       </c>
       <c r="B8">
-        <v>11028133.64162636</v>
+        <v>48939.9279780184</v>
       </c>
       <c r="C8">
-        <v>3657482.059673406</v>
+        <v>9155.819747409445</v>
       </c>
       <c r="D8">
-        <v>413865</v>
+        <v>765.2459138134806</v>
       </c>
       <c r="E8">
-        <v>14271750.70129976</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>57330.50181161436</v>
+      </c>
+      <c r="F8">
+        <v>42772.53464915186</v>
+      </c>
+      <c r="G8">
+        <v>1894.27891999393</v>
+      </c>
+      <c r="H8">
+        <v>796.9204702000263</v>
+      </c>
+      <c r="I8">
+        <v>43869.89309894577</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="2">
         <v>46295</v>
       </c>
       <c r="B9">
-        <v>10948103.24579555</v>
+        <v>48682.43072019053</v>
       </c>
       <c r="C9">
-        <v>3630939.967739111</v>
+        <v>9027.264812750194</v>
       </c>
       <c r="D9">
-        <v>486900</v>
+        <v>751.1206554578857</v>
       </c>
       <c r="E9">
-        <v>14092143.21353466</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>56958.57487748285</v>
+      </c>
+      <c r="F9">
+        <v>45840.96355198501</v>
+      </c>
+      <c r="G9">
+        <v>1874.326722251717</v>
+      </c>
+      <c r="H9">
+        <v>785.496095761579</v>
+      </c>
+      <c r="I9">
+        <v>46929.79417847515</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="2">
         <v>46387</v>
       </c>
       <c r="B10">
-        <v>10868653.62495939</v>
+        <v>48261.16099328058</v>
       </c>
       <c r="C10">
-        <v>3604590.489912759</v>
+        <v>8894.265075692938</v>
       </c>
       <c r="D10">
-        <v>559935</v>
+        <v>737.0571854750073</v>
       </c>
       <c r="E10">
-        <v>13913309.11487215</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>56418.36888349851</v>
+      </c>
+      <c r="F10">
+        <v>37473.94239427127</v>
+      </c>
+      <c r="G10">
+        <v>1861.142064047309</v>
+      </c>
+      <c r="H10">
+        <v>775.889461735457</v>
+      </c>
+      <c r="I10">
+        <v>38559.19499658313</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="2">
         <v>46477</v>
       </c>
       <c r="B11">
-        <v>12226162.21180853</v>
+        <v>53942.43235987714</v>
       </c>
       <c r="C11">
-        <v>3572342.136487956</v>
+        <v>8740.389436077081</v>
       </c>
       <c r="D11">
-        <v>632970</v>
+        <v>722.2052484386081</v>
       </c>
       <c r="E11">
-        <v>15165534.34829649</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>61960.61654751561</v>
+      </c>
+      <c r="F11">
+        <v>37060.66048428009</v>
+      </c>
+      <c r="G11">
+        <v>1849.903039751888</v>
+      </c>
+      <c r="H11">
+        <v>768.7139719489473</v>
+      </c>
+      <c r="I11">
+        <v>38141.84955208303</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="2">
         <v>46568</v>
       </c>
       <c r="B12">
-        <v>12106436.69317507</v>
+        <v>53055.94896701699</v>
       </c>
       <c r="C12">
-        <v>3537359.735010075</v>
+        <v>8575.391652865419</v>
       </c>
       <c r="D12">
-        <v>706005</v>
+        <v>705.7488848980454</v>
       </c>
       <c r="E12">
-        <v>14937791.42818515</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>60925.59173498435</v>
+      </c>
+      <c r="F12">
+        <v>37745.95119167821</v>
+      </c>
+      <c r="G12">
+        <v>1837.523470963457</v>
+      </c>
+      <c r="H12">
+        <v>761.3991068571646</v>
+      </c>
+      <c r="I12">
+        <v>38822.0755557845</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="2">
         <v>46660</v>
       </c>
       <c r="B13">
-        <v>11987883.5947634</v>
+        <v>52045.04659788643</v>
       </c>
       <c r="C13">
-        <v>3502719.901059715</v>
+        <v>8409.273936094329</v>
       </c>
       <c r="D13">
-        <v>779040</v>
+        <v>689.5792245354651</v>
       </c>
       <c r="E13">
-        <v>14711563.49582312</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>59764.74130944529</v>
+      </c>
+      <c r="F13">
+        <v>38334.98667601531</v>
+      </c>
+      <c r="G13">
+        <v>1823.98058684831</v>
+      </c>
+      <c r="H13">
+        <v>753.7307983678604</v>
+      </c>
+      <c r="I13">
+        <v>39405.23646449576</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="2">
         <v>46752</v>
       </c>
       <c r="B14">
-        <v>11870491.43556938</v>
+        <v>50938.67230294189</v>
       </c>
       <c r="C14">
-        <v>3468419.280021244</v>
+        <v>8243.099285328151</v>
       </c>
       <c r="D14">
-        <v>852075</v>
+        <v>673.7367601208989</v>
       </c>
       <c r="E14">
-        <v>14486835.71559062</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+        <v>58508.03482814915</v>
+      </c>
+      <c r="F14">
+        <v>38826.83697567004</v>
+      </c>
+      <c r="G14">
+        <v>1809.376619244432</v>
+      </c>
+      <c r="H14">
+        <v>745.7436608178608</v>
+      </c>
+      <c r="I14">
+        <v>39890.46993409662</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="2">
         <v>46843</v>
       </c>
       <c r="B15">
-        <v>13302963.028826</v>
+        <v>56246.41072830227</v>
       </c>
       <c r="C15">
-        <v>3427884.173761686</v>
+        <v>8058.145714430064</v>
       </c>
       <c r="D15">
-        <v>925110</v>
+        <v>657.3111240731066</v>
       </c>
       <c r="E15">
-        <v>15805737.20258768</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+        <v>63647.24531865922</v>
+      </c>
+      <c r="F15">
+        <v>39235.10349018065</v>
+      </c>
+      <c r="G15">
+        <v>1793.801242232153</v>
+      </c>
+      <c r="H15">
+        <v>737.4719206187901</v>
+      </c>
+      <c r="I15">
+        <v>40291.43281179401</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="2">
         <v>46934</v>
       </c>
       <c r="B16">
-        <v>13134863.04421388</v>
+        <v>54648.51577312959</v>
       </c>
       <c r="C16">
-        <v>3384568.464651405</v>
+        <v>7865.572402408403</v>
       </c>
       <c r="D16">
-        <v>998145</v>
+        <v>639.4615816326532</v>
       </c>
       <c r="E16">
-        <v>15521286.50886529</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>61874.62659390534</v>
+      </c>
+      <c r="F16">
+        <v>39583.20077841813</v>
+      </c>
+      <c r="G16">
+        <v>1777.301561523413</v>
+      </c>
+      <c r="H16">
+        <v>728.9484327379996</v>
+      </c>
+      <c r="I16">
+        <v>40631.55390720355</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="2">
         <v>47026</v>
       </c>
       <c r="B17">
-        <v>12968887.21831478</v>
+        <v>53006.00350415047</v>
       </c>
       <c r="C17">
-        <v>3341800.105031542</v>
+        <v>7676.124500143271</v>
       </c>
       <c r="D17">
-        <v>1071180</v>
+        <v>622.1517833513271</v>
       </c>
       <c r="E17">
-        <v>15239507.32334632</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>60059.97622094242</v>
+      </c>
+      <c r="F17">
+        <v>39862.01463907308</v>
+      </c>
+      <c r="G17">
+        <v>1759.947826161527</v>
+      </c>
+      <c r="H17">
+        <v>720.1984276241892</v>
+      </c>
+      <c r="I17">
+        <v>40901.76403761042</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="2">
         <v>47118</v>
       </c>
       <c r="B18">
-        <v>12805008.7096614</v>
+        <v>51341.04612656525</v>
       </c>
       <c r="C18">
-        <v>3299572.178439901</v>
+        <v>7490.42897252351</v>
       </c>
       <c r="D18">
-        <v>1144215</v>
+        <v>605.3942791925629</v>
       </c>
       <c r="E18">
-        <v>14960365.8881013</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>58226.0808198962</v>
+      </c>
+      <c r="F18">
+        <v>40070.67131567891</v>
+      </c>
+      <c r="G18">
+        <v>1741.820224967965</v>
+      </c>
+      <c r="H18">
+        <v>711.2446914341891</v>
+      </c>
+      <c r="I18">
+        <v>41101.24684921269</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="2">
         <v>47208</v>
       </c>
       <c r="B19">
-        <v>14294181.14308047</v>
+        <v>56105.35994812216</v>
       </c>
       <c r="C19">
-        <v>3250868.806609551</v>
+        <v>7288.678665014424</v>
       </c>
       <c r="D19">
-        <v>1217250</v>
+        <v>588.2578110445982</v>
       </c>
       <c r="E19">
-        <v>16327799.94969002</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>62805.78080209198</v>
+      </c>
+      <c r="F19">
+        <v>40473.6638377741</v>
+      </c>
+      <c r="G19">
+        <v>1722.780102587416</v>
+      </c>
+      <c r="H19">
+        <v>702.0765480260256</v>
+      </c>
+      <c r="I19">
+        <v>41494.36739233549</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="2">
         <v>47299</v>
       </c>
       <c r="B20">
-        <v>14067961.66509305</v>
+        <v>53964.86037297404</v>
       </c>
       <c r="C20">
-        <v>3199420.609817057</v>
+        <v>7082.626834600123</v>
       </c>
       <c r="D20">
-        <v>1290285</v>
+        <v>569.9088291393082</v>
       </c>
       <c r="E20">
-        <v>15977097.27491011</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>60477.57837843486</v>
+      </c>
+      <c r="F20">
+        <v>40515.81990168203</v>
+      </c>
+      <c r="G20">
+        <v>1703.055433386962</v>
+      </c>
+      <c r="H20">
+        <v>692.6851073928622</v>
+      </c>
+      <c r="I20">
+        <v>41526.19022767612</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="2">
         <v>47391</v>
       </c>
       <c r="B21">
-        <v>13845322.33288025</v>
+        <v>51856.83620906493</v>
       </c>
       <c r="C21">
-        <v>3148786.631349158</v>
+        <v>6883.083216470744</v>
       </c>
       <c r="D21">
-        <v>1363320</v>
+        <v>552.2953666495948</v>
       </c>
       <c r="E21">
-        <v>15630788.96422941</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>58187.62405888608</v>
+      </c>
+      <c r="F21">
+        <v>40489.9549799091</v>
+      </c>
+      <c r="G21">
+        <v>1682.84933655308</v>
+      </c>
+      <c r="H21">
+        <v>683.1639642943445</v>
+      </c>
+      <c r="I21">
+        <v>41489.64035216783</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="2">
         <v>47483</v>
       </c>
       <c r="B22">
-        <v>13626206.48711333</v>
+        <v>49794.85265398263</v>
       </c>
       <c r="C22">
-        <v>3098953.98539991</v>
+        <v>6690.243155890887</v>
       </c>
       <c r="D22">
-        <v>1436355</v>
+        <v>535.4030434557731</v>
       </c>
       <c r="E22">
-        <v>15288805.47251324</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+        <v>55949.69276641773</v>
+      </c>
+      <c r="F22">
+        <v>40402.55409642172</v>
+      </c>
+      <c r="G22">
+        <v>1662.238489701538</v>
+      </c>
+      <c r="H22">
+        <v>673.5362076238533</v>
+      </c>
+      <c r="I22">
+        <v>41391.25637849941</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" s="2">
         <v>47573</v>
       </c>
       <c r="B23">
-        <v>15138441.75742173</v>
+        <v>53789.53082815788</v>
       </c>
       <c r="C23">
-        <v>3042568.796137874</v>
+        <v>6484.878324134612</v>
       </c>
       <c r="D23">
-        <v>1509390</v>
+        <v>518.3323921091162</v>
       </c>
       <c r="E23">
-        <v>16671620.55355961</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+        <v>59756.07676018336</v>
+      </c>
+      <c r="F23">
+        <v>40481.47196813769</v>
+      </c>
+      <c r="G23">
+        <v>1641.283557031918</v>
+      </c>
+      <c r="H23">
+        <v>663.7649617265754</v>
+      </c>
+      <c r="I23">
+        <v>41458.99056344303</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" s="2">
         <v>47664</v>
       </c>
       <c r="B24">
-        <v>14844994.50063836</v>
+        <v>51305.49307282426</v>
       </c>
       <c r="C24">
-        <v>2983590.898603365</v>
+        <v>6278.312962724332</v>
       </c>
       <c r="D24">
-        <v>1582425</v>
+        <v>500.3000960026811</v>
       </c>
       <c r="E24">
-        <v>16246160.39924173</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+        <v>57083.50593954591</v>
+      </c>
+      <c r="F24">
+        <v>40280.62254284001</v>
+      </c>
+      <c r="G24">
+        <v>1620.053094936677</v>
+      </c>
+      <c r="H24">
+        <v>653.8114181654762</v>
+      </c>
+      <c r="I24">
+        <v>41246.86421961121</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" s="2">
         <v>47756</v>
       </c>
       <c r="B25">
-        <v>14557235.49723625</v>
+        <v>48920.82328944881</v>
       </c>
       <c r="C25">
-        <v>2925756.243056353</v>
+        <v>6080.571853420745</v>
       </c>
       <c r="D25">
-        <v>1655460</v>
+        <v>483.1314167904911</v>
       </c>
       <c r="E25">
-        <v>15827531.74029261</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>54518.26372607907</v>
+      </c>
+      <c r="F25">
+        <v>40042.39754454989</v>
+      </c>
+      <c r="G25">
+        <v>1598.599562534792</v>
+      </c>
+      <c r="H25">
+        <v>643.808420852</v>
+      </c>
+      <c r="I25">
+        <v>40997.18868623268</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" s="2">
         <v>47848</v>
       </c>
       <c r="B26">
-        <v>14275054.48472093</v>
+        <v>46639.4544314648</v>
       </c>
       <c r="C26">
-        <v>2869042.668614597</v>
+        <v>5891.467609969285</v>
       </c>
       <c r="D26">
-        <v>1728495</v>
+        <v>466.7887372770358</v>
       </c>
       <c r="E26">
-        <v>15415602.15333552</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>52064.13330415705</v>
+      </c>
+      <c r="F26">
+        <v>39770.90004647928</v>
+      </c>
+      <c r="G26">
+        <v>1576.964279243188</v>
+      </c>
+      <c r="H26">
+        <v>633.7710017769549</v>
+      </c>
+      <c r="I26">
+        <v>40714.09332394552</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" s="2">
         <v>47938</v>
       </c>
       <c r="B27">
-        <v>15756636.48327765</v>
+        <v>72470.12125471454</v>
       </c>
       <c r="C27">
-        <v>2805951.634295124</v>
+        <v>5543.39759941953</v>
       </c>
       <c r="D27">
-        <v>1801530</v>
+        <v>444.4183215222026</v>
       </c>
       <c r="E27">
-        <v>16761058.11757277</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
+        <v>77569.10053261186</v>
+      </c>
+      <c r="F27">
+        <v>40101.35040768915</v>
+      </c>
+      <c r="G27">
+        <v>1554.652348877225</v>
+      </c>
+      <c r="H27">
+        <v>623.6320280853033</v>
+      </c>
+      <c r="I27">
+        <v>41032.37072848107</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" s="2">
         <v>48029</v>
       </c>
       <c r="B28">
-        <v>15389505.92697919</v>
+        <v>44689.87984585458</v>
       </c>
       <c r="C28">
-        <v>2740572.796270992</v>
+        <v>5360.285072586859</v>
       </c>
       <c r="D28">
-        <v>1874565</v>
+        <v>425.0962919584548</v>
       </c>
       <c r="E28">
-        <v>16255513.72325018</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
+        <v>49625.06862648298</v>
+      </c>
+      <c r="F28">
+        <v>39701.92534498344</v>
+      </c>
+      <c r="G28">
+        <v>1532.028925484398</v>
+      </c>
+      <c r="H28">
+        <v>613.3369801038484</v>
+      </c>
+      <c r="I28">
+        <v>40620.61729036399</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29" s="2">
         <v>48121</v>
       </c>
       <c r="B29">
-        <v>15030929.53422389</v>
+        <v>42406.83344083834</v>
       </c>
       <c r="C29">
-        <v>2676717.289016052</v>
+        <v>5186.227852249795</v>
       </c>
       <c r="D29">
-        <v>1947600</v>
+        <v>409.802424145025</v>
       </c>
       <c r="E29">
-        <v>15760046.82323994</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
+        <v>47183.25886894311</v>
+      </c>
+      <c r="F29">
+        <v>39277.47113536802</v>
+      </c>
+      <c r="G29">
+        <v>1509.413471546636</v>
+      </c>
+      <c r="H29">
+        <v>603.0702539578369</v>
+      </c>
+      <c r="I29">
+        <v>40183.81435295682</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
       <c r="A30" s="2">
         <v>48213</v>
       </c>
       <c r="B30">
-        <v>14680707.99249834</v>
+        <v>40267.36404561292</v>
       </c>
       <c r="C30">
-        <v>2614349.618833834</v>
+        <v>5020.716434282385</v>
       </c>
       <c r="D30">
-        <v>2020635</v>
+        <v>395.3119882176489</v>
       </c>
       <c r="E30">
-        <v>15274422.61133217</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
+        <v>44892.76849167766</v>
+      </c>
+      <c r="F30">
+        <v>38786.5272713365</v>
+      </c>
+      <c r="G30">
+        <v>1251.435601535325</v>
+      </c>
+      <c r="H30">
+        <v>594.0973450599033</v>
+      </c>
+      <c r="I30">
+        <v>39443.86552781193</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
       <c r="A31" s="2">
         <v>48304</v>
       </c>
       <c r="B31">
-        <v>16096665.3511734</v>
+        <v>51724.26885400909</v>
       </c>
       <c r="C31">
-        <v>2545952.38108688</v>
+        <v>4848.512514447999</v>
       </c>
       <c r="D31">
-        <v>2093670</v>
+        <v>376.1901060943635</v>
       </c>
       <c r="E31">
-        <v>16548947.73226028</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
+        <v>56196.59126236272</v>
+      </c>
+      <c r="F31">
+        <v>38218.80274329489</v>
+      </c>
+      <c r="G31">
+        <v>1118.233123049143</v>
+      </c>
+      <c r="H31">
+        <v>586.4531084865722</v>
+      </c>
+      <c r="I31">
+        <v>38750.58275785746</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
       <c r="A32" s="2">
         <v>48395</v>
       </c>
       <c r="B32">
-        <v>15652357.47536033</v>
+        <v>38991.02963879679</v>
       </c>
       <c r="C32">
-        <v>2475677.782610527</v>
+        <v>4678.162873396834</v>
       </c>
       <c r="D32">
-        <v>2166705</v>
+        <v>359.7129472173858</v>
       </c>
       <c r="E32">
-        <v>15961330.25797086</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
+        <v>43309.47956497624</v>
+      </c>
+      <c r="F32">
+        <v>37646.74501425802</v>
+      </c>
+      <c r="G32">
+        <v>1104.12253683295</v>
+      </c>
+      <c r="H32">
+        <v>576.3452423140457</v>
+      </c>
+      <c r="I32">
+        <v>38174.52230877693</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
       <c r="A33" s="2">
         <v>48487</v>
       </c>
       <c r="B33">
-        <v>15220313.5985932</v>
+        <v>36977.14662305031</v>
       </c>
       <c r="C33">
-        <v>2407342.937299905</v>
+        <v>4516.942842448479</v>
       </c>
       <c r="D33">
-        <v>2239740</v>
+        <v>346.4857125911441</v>
       </c>
       <c r="E33">
-        <v>15387916.5358931</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
+        <v>41147.60375290764</v>
+      </c>
+      <c r="F33">
+        <v>37056.36584642121</v>
+      </c>
+      <c r="G33">
+        <v>1090.013263051261</v>
+      </c>
+      <c r="H33">
+        <v>566.2790372353879</v>
+      </c>
+      <c r="I33">
+        <v>37580.10007223708</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
       <c r="A34" s="2">
         <v>48579</v>
       </c>
       <c r="B34">
-        <v>14800195.20408941</v>
+        <v>35082.23213645752</v>
       </c>
       <c r="C34">
-        <v>2340894.303157968</v>
+        <v>4364.295489281479</v>
       </c>
       <c r="D34">
-        <v>2312775</v>
+        <v>333.9322646789794</v>
       </c>
       <c r="E34">
-        <v>14828314.50724738</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
+        <v>39112.59536106002</v>
+      </c>
+      <c r="F34">
+        <v>36572.58751527245</v>
+      </c>
+      <c r="G34">
+        <v>1075.925085328823</v>
+      </c>
+      <c r="H34">
+        <v>556.2649080688198</v>
+      </c>
+      <c r="I34">
+        <v>37092.24769253246</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
       <c r="A35" s="2">
         <v>48669</v>
       </c>
       <c r="B35">
-        <v>16126901.62012396</v>
+        <v>37088.51261273944</v>
       </c>
       <c r="C35">
-        <v>2268886.315625245</v>
+        <v>4206.543025757619</v>
       </c>
       <c r="D35">
-        <v>2385810</v>
+        <v>321.4559243730718</v>
       </c>
       <c r="E35">
-        <v>16009977.93574921</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
+        <v>40973.59971412399</v>
+      </c>
+      <c r="F35">
+        <v>36358.46957010085</v>
+      </c>
+      <c r="G35">
+        <v>1061.728118659727</v>
+      </c>
+      <c r="H35">
+        <v>546.2889390678154</v>
+      </c>
+      <c r="I35">
+        <v>36873.90874969276</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36" s="2">
         <v>48760</v>
       </c>
       <c r="B36">
-        <v>15605159.77729292</v>
+        <v>34991.22282473747</v>
       </c>
       <c r="C36">
-        <v>2195482.697535873</v>
+        <v>4051.327272070775</v>
       </c>
       <c r="D36">
-        <v>2458845</v>
+        <v>308.5551108719518</v>
       </c>
       <c r="E36">
-        <v>15341797.47482879</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
+        <v>38733.99498593629</v>
+      </c>
+      <c r="F36">
+        <v>35620.47461093841</v>
+      </c>
+      <c r="G36">
+        <v>1047.598386872075</v>
+      </c>
+      <c r="H36">
+        <v>536.3562964806233</v>
+      </c>
+      <c r="I36">
+        <v>36131.71670132987</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
       <c r="A37" s="2">
         <v>48852</v>
       </c>
       <c r="B37">
-        <v>15100297.46637525</v>
+        <v>33030.01128985747</v>
       </c>
       <c r="C37">
-        <v>2124453.85296931</v>
+        <v>3905.06407275828</v>
       </c>
       <c r="D37">
-        <v>2531880</v>
+        <v>296.3771931305957</v>
       </c>
       <c r="E37">
-        <v>14692871.31934456</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
+        <v>36638.69816948516</v>
+      </c>
+      <c r="F37">
+        <v>34892.10256125899</v>
+      </c>
+      <c r="G37">
+        <v>1033.634840792557</v>
+      </c>
+      <c r="H37">
+        <v>526.5338853776092</v>
+      </c>
+      <c r="I37">
+        <v>35399.20351667394</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
       <c r="A38" s="2">
         <v>48944</v>
       </c>
       <c r="B38">
-        <v>14611768.59623119</v>
+        <v>31195.34228826148</v>
       </c>
       <c r="C38">
-        <v>2055722.952616165</v>
+        <v>3767.161567058252</v>
       </c>
       <c r="D38">
-        <v>2604915</v>
+        <v>284.8769706556972</v>
       </c>
       <c r="E38">
-        <v>14062576.54884736</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
+        <v>34677.62688466403</v>
+      </c>
+      <c r="F38">
+        <v>34173.95491299894</v>
+      </c>
+      <c r="G38">
+        <v>1019.835147442678</v>
+      </c>
+      <c r="H38">
+        <v>516.8234387593609</v>
+      </c>
+      <c r="I38">
+        <v>34676.96662168226</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
       <c r="A39" s="2">
         <v>49034</v>
       </c>
       <c r="B39">
-        <v>15821367.50327947</v>
+        <v>32742.0167782819</v>
       </c>
       <c r="C39">
-        <v>1982039.193547465</v>
+        <v>3625.611959168747</v>
       </c>
       <c r="D39">
-        <v>2677950</v>
+        <v>273.5269604460032</v>
       </c>
       <c r="E39">
-        <v>15125456.69682694</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
+        <v>36094.10177700465</v>
+      </c>
+      <c r="F39">
+        <v>33480.95884043734</v>
+      </c>
+      <c r="G39">
+        <v>1006.189928318395</v>
+      </c>
+      <c r="H39">
+        <v>507.2263880889509</v>
+      </c>
+      <c r="I39">
+        <v>33979.92238066678</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
       <c r="A40" s="2">
         <v>49125</v>
       </c>
       <c r="B40">
-        <v>15226409.47038277</v>
+        <v>30749.73162651838</v>
       </c>
       <c r="C40">
-        <v>1907505.17242238</v>
+        <v>3487.070786760622</v>
       </c>
       <c r="D40">
-        <v>2750985</v>
+        <v>261.8903133573332</v>
       </c>
       <c r="E40">
-        <v>14382929.64280515</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
+        <v>33974.91209992167</v>
+      </c>
+      <c r="F40">
+        <v>32827.31543562462</v>
+      </c>
+      <c r="G40">
+        <v>992.6627327202319</v>
+      </c>
+      <c r="H40">
+        <v>497.7416671849744</v>
+      </c>
+      <c r="I40">
+        <v>33322.23650115987</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
       <c r="A41" s="2">
         <v>49217</v>
       </c>
       <c r="B41">
-        <v>14653824.66539035</v>
+        <v>28898.21286090586</v>
       </c>
       <c r="C41">
-        <v>1835773.981999715</v>
+        <v>3357.050014468295</v>
       </c>
       <c r="D41">
-        <v>2824020</v>
+        <v>250.9613230953065</v>
       </c>
       <c r="E41">
-        <v>13665578.64739007</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
+        <v>32004.30155227884</v>
+      </c>
+      <c r="F41">
+        <v>32183.43695121452</v>
+      </c>
+      <c r="G41">
+        <v>979.2456819779948</v>
+      </c>
+      <c r="H41">
+        <v>488.3685648126933</v>
+      </c>
+      <c r="I41">
+        <v>32674.31406837982</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
       <c r="A42" s="2">
         <v>49309</v>
       </c>
       <c r="B42">
-        <v>14102771.74941918</v>
+        <v>27176.79556564071</v>
       </c>
       <c r="C42">
-        <v>1766740.222626696</v>
+        <v>3234.94022445521</v>
       </c>
       <c r="D42">
-        <v>2897055</v>
+        <v>240.6917574825704</v>
       </c>
       <c r="E42">
-        <v>12972456.97204587</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
+        <v>30171.04403261335</v>
+      </c>
+      <c r="F42">
+        <v>31548.97957416131</v>
+      </c>
+      <c r="G42">
+        <v>965.9390585618074</v>
+      </c>
+      <c r="H42">
+        <v>479.1078331773699</v>
+      </c>
+      <c r="I42">
+        <v>32035.81079954575</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
       <c r="A43" s="2">
         <v>49399</v>
       </c>
       <c r="B43">
-        <v>15083354.9516884</v>
+        <v>32943.58602786779</v>
       </c>
       <c r="C43">
-        <v>1693849.039354988</v>
+        <v>3079.730379521057</v>
       </c>
       <c r="D43">
-        <v>2970090</v>
+        <v>229.3803648667102</v>
       </c>
       <c r="E43">
-        <v>13807113.99104339</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
+        <v>35793.93604252215</v>
+      </c>
+      <c r="F43">
+        <v>30991.91680069574</v>
+      </c>
+      <c r="G43">
+        <v>952.6944639913861</v>
+      </c>
+      <c r="H43">
+        <v>469.9514454796911</v>
+      </c>
+      <c r="I43">
+        <v>31474.65981920743</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
       <c r="A44" s="2">
         <v>49490</v>
       </c>
       <c r="B44">
-        <v>14433206.52576444</v>
+        <v>25883.03855374209</v>
       </c>
       <c r="C44">
-        <v>1620837.876373228</v>
+        <v>2962.381648453919</v>
       </c>
       <c r="D44">
-        <v>3043125</v>
+        <v>218.7195052166481</v>
       </c>
       <c r="E44">
-        <v>13010919.40213766</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
+        <v>28626.70069697936</v>
+      </c>
+      <c r="F44">
+        <v>30368.87263070798</v>
+      </c>
+      <c r="G44">
+        <v>799.1122383675054</v>
+      </c>
+      <c r="H44">
+        <v>460.8858000966408</v>
+      </c>
+      <c r="I44">
+        <v>30707.09906897884</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
       <c r="A45" s="2">
         <v>49582</v>
       </c>
       <c r="B45">
-        <v>13811081.90336994</v>
+        <v>24279.35379184559</v>
       </c>
       <c r="C45">
-        <v>1550973.764749704</v>
+        <v>2852.311947694847</v>
       </c>
       <c r="D45">
-        <v>3116160</v>
+        <v>209.3588348797884</v>
       </c>
       <c r="E45">
-        <v>12245895.66811965</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
+        <v>26922.30690466065</v>
+      </c>
+      <c r="F45">
+        <v>29676.31542814702</v>
+      </c>
+      <c r="G45">
+        <v>513.2152931532607</v>
+      </c>
+      <c r="H45">
+        <v>458.7534788258488</v>
+      </c>
+      <c r="I45">
+        <v>29730.77724247443</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
       <c r="A46" s="2">
         <v>49674</v>
       </c>
       <c r="B46">
-        <v>13215773.15484926</v>
+        <v>22792.06386893861</v>
       </c>
       <c r="C46">
-        <v>1484121.054922802</v>
+        <v>2748.99693306276</v>
       </c>
       <c r="D46">
-        <v>3189195</v>
+        <v>200.5873791709211</v>
       </c>
       <c r="E46">
-        <v>11510699.20977206</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
+        <v>25340.47342283044</v>
+      </c>
+      <c r="F46">
+        <v>28971.95906629915</v>
+      </c>
+      <c r="G46">
+        <v>512.2577844135137</v>
+      </c>
+      <c r="H46">
+        <v>449.8658201923616</v>
+      </c>
+      <c r="I46">
+        <v>29034.35103052031</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
       <c r="A47" s="2">
         <v>49765</v>
       </c>
       <c r="B47">
-        <v>14035600.13207752</v>
+        <v>23774.96013237627</v>
       </c>
       <c r="C47">
-        <v>1414207.097611185</v>
+        <v>2643.455286729988</v>
       </c>
       <c r="D47">
-        <v>3262230</v>
+        <v>192.0077384806727</v>
       </c>
       <c r="E47">
-        <v>12187577.2296887</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
+        <v>26226.40768062558</v>
+      </c>
+      <c r="F47">
+        <v>28273.82815622649</v>
+      </c>
+      <c r="G47">
+        <v>511.2753674887214</v>
+      </c>
+      <c r="H47">
+        <v>441.0800865126629</v>
+      </c>
+      <c r="I47">
+        <v>28344.02343720255</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
       <c r="A48" s="2">
         <v>49856</v>
       </c>
       <c r="B48">
-        <v>13345955.43809378</v>
+        <v>22199.13876462779</v>
       </c>
       <c r="C48">
-        <v>1344719.479562512</v>
+        <v>2540.584504621659</v>
       </c>
       <c r="D48">
-        <v>3335265</v>
+        <v>183.2967598841566</v>
       </c>
       <c r="E48">
-        <v>11355409.91765629</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
+        <v>24556.42650936529</v>
+      </c>
+      <c r="F48">
+        <v>27576.60584939935</v>
+      </c>
+      <c r="G48">
+        <v>510.2784335835407</v>
+      </c>
+      <c r="H48">
+        <v>432.399658938764</v>
+      </c>
+      <c r="I48">
+        <v>27654.48462404412</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
       <c r="A49" s="2">
         <v>49948</v>
       </c>
       <c r="B49">
-        <v>12690196.70548428</v>
+        <v>20748.93899424379</v>
       </c>
       <c r="C49">
-        <v>1278646.162764509</v>
+        <v>2444.400816984183</v>
       </c>
       <c r="D49">
-        <v>3408300</v>
+        <v>175.1785238156021</v>
       </c>
       <c r="E49">
-        <v>10560542.86824879</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
+        <v>23018.16128741237</v>
+      </c>
+      <c r="F49">
+        <v>27522.19769909307</v>
+      </c>
+      <c r="G49">
+        <v>509.2629518630887</v>
+      </c>
+      <c r="H49">
+        <v>423.8269885910187</v>
+      </c>
+      <c r="I49">
+        <v>27607.63366236514</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
       <c r="A50" s="2">
         <v>50040</v>
       </c>
       <c r="B50">
-        <v>12066658.93430302</v>
+        <v>19413.8981217065</v>
       </c>
       <c r="C50">
-        <v>1215819.384191793</v>
+        <v>2354.377616937946</v>
       </c>
       <c r="D50">
-        <v>3481335</v>
+        <v>167.6070017721683</v>
       </c>
       <c r="E50">
-        <v>9801143.318494808</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
+        <v>21600.66873687229</v>
+      </c>
+      <c r="F50">
+        <v>26855.69997163772</v>
+      </c>
+      <c r="G50">
+        <v>508.2216347463757</v>
+      </c>
+      <c r="H50">
+        <v>415.3633902792338</v>
+      </c>
+      <c r="I50">
+        <v>26948.55821610486</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
       <c r="A51" s="2">
         <v>50130</v>
       </c>
       <c r="B51">
-        <v>12716950.55571419</v>
+        <v>20223.36266634782</v>
       </c>
       <c r="C51">
-        <v>1150754.409164251</v>
+        <v>2262.544790876508</v>
       </c>
       <c r="D51">
-        <v>3554370</v>
+        <v>160.2333837553965</v>
       </c>
       <c r="E51">
-        <v>10313334.96487844</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
+        <v>22325.67407346893</v>
+      </c>
+      <c r="F51">
+        <v>26220.2299597321</v>
+      </c>
+      <c r="G51">
+        <v>507.1430418039417</v>
+      </c>
+      <c r="H51">
+        <v>407.0102760013118</v>
+      </c>
+      <c r="I51">
+        <v>26320.36272553472</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
       <c r="A52" s="2">
         <v>50221</v>
       </c>
       <c r="B52">
-        <v>12008144.59098631</v>
+        <v>18829.28680782588</v>
       </c>
       <c r="C52">
-        <v>1086614.693783663</v>
+        <v>2173.187159789259</v>
       </c>
       <c r="D52">
-        <v>3627405</v>
+        <v>152.7765773972956</v>
       </c>
       <c r="E52">
-        <v>9467354.284769971</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
+        <v>20849.69739021785</v>
+      </c>
+      <c r="F52">
+        <v>25629.88490161331</v>
+      </c>
+      <c r="G52">
+        <v>505.9989092790539</v>
+      </c>
+      <c r="H52">
+        <v>398.7701014827782</v>
+      </c>
+      <c r="I52">
+        <v>25737.11370940958</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
       <c r="A53" s="2">
         <v>50313</v>
       </c>
       <c r="B53">
-        <v>11338845.41630473</v>
+        <v>17555.86581864425</v>
       </c>
       <c r="C53">
-        <v>1026049.940233627</v>
+        <v>2089.797839767918</v>
       </c>
       <c r="D53">
-        <v>3700440</v>
+        <v>145.8559739933466</v>
       </c>
       <c r="E53">
-        <v>8664455.356538357</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
+        <v>19499.80768441883</v>
+      </c>
+      <c r="F53">
+        <v>25051.33307983458</v>
+      </c>
+      <c r="G53">
+        <v>504.7794054487211</v>
+      </c>
+      <c r="H53">
+        <v>390.6443821107559</v>
+      </c>
+      <c r="I53">
+        <v>25165.46810317254</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
       <c r="A54" s="2">
         <v>50405</v>
       </c>
       <c r="B54">
-        <v>10706851.03770012</v>
+        <v>16391.99753107921</v>
       </c>
       <c r="C54">
-        <v>968860.890503502</v>
+        <v>2011.868656038965</v>
       </c>
       <c r="D54">
-        <v>3773475</v>
+        <v>139.425960705757</v>
       </c>
       <c r="E54">
-        <v>7902236.928203622</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
+        <v>18264.44022641241</v>
+      </c>
+      <c r="F54">
+        <v>24484.46930840481</v>
+      </c>
+      <c r="G54">
+        <v>503.4799002749239</v>
+      </c>
+      <c r="H54">
+        <v>382.6337157740404</v>
+      </c>
+      <c r="I54">
+        <v>24605.3154929057</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
       <c r="A55" s="2">
         <v>50495</v>
       </c>
       <c r="B55">
-        <v>11192173.8075622</v>
+        <v>17077.97696399041</v>
       </c>
       <c r="C55">
-        <v>910216.5167417477</v>
+        <v>1932.352333739619</v>
       </c>
       <c r="D55">
-        <v>3846510</v>
+        <v>133.1843755624234</v>
       </c>
       <c r="E55">
-        <v>8255880.324303949</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
+        <v>18877.1449221676</v>
+      </c>
+      <c r="F55">
+        <v>23915.4071362474</v>
+      </c>
+      <c r="G55">
+        <v>502.093220749024</v>
+      </c>
+      <c r="H55">
+        <v>374.7392490158279</v>
+      </c>
+      <c r="I55">
+        <v>24042.76110798059</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
       <c r="A56" s="2">
         <v>50586</v>
       </c>
       <c r="B56">
-        <v>10487457.75645303</v>
+        <v>15879.09910340303</v>
       </c>
       <c r="C56">
-        <v>852904.666482669</v>
+        <v>1854.983859514578</v>
       </c>
       <c r="D56">
-        <v>3919545</v>
+        <v>126.8888996909759</v>
       </c>
       <c r="E56">
-        <v>7420817.422935698</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
+        <v>17607.19406322663</v>
+      </c>
+      <c r="F56">
+        <v>23334.03167021302</v>
+      </c>
+      <c r="G56">
+        <v>500.6013465510952</v>
+      </c>
+      <c r="H56">
+        <v>366.9700052189276</v>
+      </c>
+      <c r="I56">
+        <v>23467.66301154519</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
       <c r="A57" s="2">
         <v>50678</v>
       </c>
       <c r="B57">
-        <v>9827114.203593966</v>
+        <v>14791.36373436761</v>
       </c>
       <c r="C57">
-        <v>799201.4611115966</v>
+        <v>1782.805395499084</v>
       </c>
       <c r="D57">
-        <v>3992580</v>
+        <v>121.0625227115483</v>
       </c>
       <c r="E57">
-        <v>6633735.664705561</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
+        <v>16453.10660715515</v>
+      </c>
+      <c r="F57">
+        <v>22770.60194423276</v>
+      </c>
+      <c r="G57">
+        <v>498.9978111564897</v>
+      </c>
+      <c r="H57">
+        <v>359.3302880388188</v>
+      </c>
+      <c r="I57">
+        <v>22910.26946735043</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
       <c r="A58" s="2">
         <v>50770</v>
       </c>
       <c r="B58">
-        <v>9208349.231352704</v>
+        <v>13803.53710565196</v>
       </c>
       <c r="C58">
-        <v>748879.6820364092</v>
+        <v>1715.346813026951</v>
       </c>
       <c r="D58">
-        <v>4065615</v>
+        <v>115.6620079015468</v>
       </c>
       <c r="E58">
-        <v>5891613.913389113</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
+        <v>15403.22191077736</v>
+      </c>
+      <c r="F58">
+        <v>22224.64957379006</v>
+      </c>
+      <c r="G58">
+        <v>497.2795633533318</v>
+      </c>
+      <c r="H58">
+        <v>351.8185071496711</v>
+      </c>
+      <c r="I58">
+        <v>22370.11062999372</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
       <c r="A59" s="2">
         <v>50860</v>
       </c>
       <c r="B59">
-        <v>9537075.819778142</v>
+        <v>14406.76889775483</v>
       </c>
       <c r="C59">
-        <v>697821.0574712473</v>
+        <v>1646.388295986159</v>
       </c>
       <c r="D59">
-        <v>4138650</v>
+        <v>110.4285115501761</v>
       </c>
       <c r="E59">
-        <v>6096246.877249389</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
+        <v>15942.72868219081</v>
+      </c>
+      <c r="F59">
+        <v>21689.81033142663</v>
+      </c>
+      <c r="G59">
+        <v>495.4462450540821</v>
+      </c>
+      <c r="H59">
+        <v>344.4329919333437</v>
+      </c>
+      <c r="I59">
+        <v>21840.82358454736</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
       <c r="A60" s="2">
         <v>50951</v>
       </c>
       <c r="B60">
-        <v>8861498.950192727</v>
+        <v>13400.89602643722</v>
       </c>
       <c r="C60">
-        <v>648389.5782164063</v>
+        <v>1579.186563012977</v>
       </c>
       <c r="D60">
-        <v>4211685</v>
+        <v>105.1544112824657</v>
       </c>
       <c r="E60">
-        <v>5298203.528409134</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
+        <v>14874.92817816773</v>
+      </c>
+      <c r="F60">
+        <v>21160.4859679369</v>
+      </c>
+      <c r="G60">
+        <v>493.5063058230336</v>
+      </c>
+      <c r="H60">
+        <v>337.170151887562</v>
+      </c>
+      <c r="I60">
+        <v>21316.82212187237</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
       <c r="A61" s="2">
         <v>51043</v>
       </c>
       <c r="B61">
-        <v>8233777.850587912</v>
+        <v>12492.89416290635</v>
       </c>
       <c r="C61">
-        <v>602459.6716285989</v>
+        <v>1516.40705479721</v>
       </c>
       <c r="D61">
-        <v>4284720</v>
+        <v>100.2779019416346</v>
       </c>
       <c r="E61">
-        <v>4551517.522216512</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
+        <v>13909.02331576192</v>
+      </c>
+      <c r="F61">
+        <v>20648.60528895303</v>
+      </c>
+      <c r="G61">
+        <v>491.4598116509066</v>
+      </c>
+      <c r="H61">
+        <v>330.0275706129931</v>
+      </c>
+      <c r="I61">
+        <v>20810.03752999094</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
       <c r="A62" s="2">
         <v>51135</v>
       </c>
       <c r="B62">
-        <v>7650522.566654216</v>
+        <v>11671.9989148672</v>
       </c>
       <c r="C62">
-        <v>559783.2971610453</v>
+        <v>1457.633769462427</v>
       </c>
       <c r="D62">
-        <v>4357755</v>
+        <v>95.75993905152673</v>
       </c>
       <c r="E62">
-        <v>3852550.863815262</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
+        <v>13033.87274527809</v>
+      </c>
+      <c r="F62">
+        <v>20153.65910620395</v>
+      </c>
+      <c r="G62">
+        <v>489.3048864421367</v>
+      </c>
+      <c r="H62">
+        <v>323.0043182579961</v>
+      </c>
+      <c r="I62">
+        <v>20319.95967438809</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
       <c r="A63" s="2">
         <v>51226</v>
       </c>
       <c r="B63">
-        <v>7840285.40210523</v>
+        <v>18916.73755551449</v>
       </c>
       <c r="C63">
-        <v>516978.3862627394</v>
+        <v>1352.519597040574</v>
       </c>
       <c r="D63">
-        <v>4430790</v>
+        <v>89.55739343678172</v>
       </c>
       <c r="E63">
-        <v>3926473.788367969</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
+        <v>20179.69975911828</v>
+      </c>
+      <c r="F63">
+        <v>19744.58522876442</v>
+      </c>
+      <c r="G63">
+        <v>486.9936618137966</v>
+      </c>
+      <c r="H63">
+        <v>316.0922745398723</v>
+      </c>
+      <c r="I63">
+        <v>19915.48661603834</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
       <c r="A64" s="2">
         <v>51317</v>
       </c>
       <c r="B64">
-        <v>7218216.936361182</v>
+        <v>10400.06958970095</v>
       </c>
       <c r="C64">
-        <v>475959.9876877407</v>
+        <v>1299.709196171439</v>
       </c>
       <c r="D64">
-        <v>4503825</v>
+        <v>84.53935019515841</v>
       </c>
       <c r="E64">
-        <v>3190351.924048922</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
+        <v>11615.23943567723</v>
+      </c>
+      <c r="F64">
+        <v>19325.93509874169</v>
+      </c>
+      <c r="G64">
+        <v>484.5398847677169</v>
+      </c>
+      <c r="H64">
+        <v>309.2763923799824</v>
+      </c>
+      <c r="I64">
+        <v>19501.19859112943</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
       <c r="A65" s="2">
         <v>51409</v>
       </c>
       <c r="B65">
-        <v>6645504.987150224</v>
+        <v>9786.344688522669</v>
       </c>
       <c r="C65">
-        <v>438196.0946517847</v>
+        <v>1249.808525309716</v>
       </c>
       <c r="D65">
-        <v>4576860</v>
+        <v>80.77843395432276</v>
       </c>
       <c r="E65">
-        <v>2506841.081802009</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
+        <v>10955.37477987806</v>
+      </c>
+      <c r="F65">
+        <v>18918.01131249507</v>
+      </c>
+      <c r="G65">
+        <v>481.9633464186726</v>
+      </c>
+      <c r="H65">
+        <v>302.5652641738763</v>
+      </c>
+      <c r="I65">
+        <v>19097.40939473987</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
       <c r="A66" s="2">
         <v>51501</v>
       </c>
       <c r="B66">
-        <v>6118233.481148551</v>
+        <v>9227.080695487612</v>
       </c>
       <c r="C66">
-        <v>403428.4862912683</v>
+        <v>1202.576393458623</v>
       </c>
       <c r="D66">
-        <v>4649895</v>
+        <v>77.2678996063072</v>
       </c>
       <c r="E66">
-        <v>1871766.96743982</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
+        <v>10352.38918933993</v>
+      </c>
+      <c r="F66">
+        <v>18520.60043545165</v>
+      </c>
+      <c r="G66">
+        <v>479.2633492336734</v>
+      </c>
+      <c r="H66">
+        <v>295.95891287848</v>
+      </c>
+      <c r="I66">
+        <v>18703.90487180684</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
       <c r="A67" s="2">
         <v>51591</v>
       </c>
       <c r="B67">
-        <v>6199496.606384772</v>
+        <v>13772.4349627825</v>
       </c>
       <c r="C67">
-        <v>368973.1552415846</v>
+        <v>1153.522758770879</v>
       </c>
       <c r="D67">
-        <v>4722930</v>
+        <v>71.04643856241586</v>
       </c>
       <c r="E67">
-        <v>1845539.761626356</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
+        <v>14854.91128299097</v>
+      </c>
+      <c r="F67">
+        <v>18118.84852572613</v>
+      </c>
+      <c r="G67">
+        <v>476.4419565095745</v>
+      </c>
+      <c r="H67">
+        <v>289.4581610108447</v>
+      </c>
+      <c r="I67">
+        <v>18305.83232122486</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
       <c r="A68" s="2">
         <v>51682</v>
       </c>
       <c r="B68">
-        <v>5650766.618683459</v>
+        <v>8606.541382930112</v>
       </c>
       <c r="C68">
-        <v>336314.5947498647</v>
+        <v>1105.050410499524</v>
       </c>
       <c r="D68">
-        <v>4795965</v>
+        <v>66.61564728719779</v>
       </c>
       <c r="E68">
-        <v>1191116.213433323</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
+        <v>9644.976146142439</v>
+      </c>
+      <c r="F68">
+        <v>17701.10416380947</v>
+      </c>
+      <c r="G68">
+        <v>473.51013677854</v>
+      </c>
+      <c r="H68">
+        <v>283.0760776056393</v>
+      </c>
+      <c r="I68">
+        <v>17891.53822298237</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
       <c r="A69" s="2">
         <v>51774</v>
       </c>
       <c r="B69">
-        <v>5150605.832406111</v>
+        <v>8159.63421709794</v>
       </c>
       <c r="C69">
-        <v>306546.7095233765</v>
+        <v>1059.204139688164</v>
       </c>
       <c r="D69">
-        <v>4869000</v>
+        <v>63.84067103572965</v>
       </c>
       <c r="E69">
-        <v>588152.5419294876</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
+        <v>9154.997685750373</v>
+      </c>
+      <c r="F69">
+        <v>17298.72755479131</v>
+      </c>
+      <c r="G69">
+        <v>470.4693564093731</v>
+      </c>
+      <c r="H69">
+        <v>276.8190518183867</v>
+      </c>
+      <c r="I69">
+        <v>17492.37785938229</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
       <c r="A70" s="2">
         <v>51866</v>
       </c>
       <c r="B70">
-        <v>4694715.289267535</v>
+        <v>7746.596883606258</v>
       </c>
       <c r="C70">
-        <v>279413.6400458642</v>
+        <v>1015.775057959833</v>
       </c>
       <c r="D70">
-        <v>4942035</v>
+        <v>61.21329044425502</v>
       </c>
       <c r="E70">
-        <v>32093.9293133996</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
+        <v>8701.158651121836</v>
+      </c>
+      <c r="F70">
+        <v>16911.11638368313</v>
+      </c>
+      <c r="G70">
+        <v>467.318929966317</v>
+      </c>
+      <c r="H70">
+        <v>270.6845539236303</v>
+      </c>
+      <c r="I70">
+        <v>17107.75075972582</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
       <c r="A71" s="2">
         <v>51956</v>
       </c>
       <c r="B71">
-        <v>4704469.773896562</v>
+        <v>15314.05668101626</v>
       </c>
       <c r="C71">
-        <v>252841.8715418353</v>
+        <v>923.6608780022342</v>
       </c>
       <c r="D71">
-        <v>5015070</v>
+        <v>56.69599010880465</v>
       </c>
       <c r="E71">
-        <v>-57758.35456160293</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
+        <v>16181.02156890969</v>
+      </c>
+      <c r="F71">
+        <v>16654.68483405611</v>
+      </c>
+      <c r="G71">
+        <v>463.9590290055469</v>
+      </c>
+      <c r="H71">
+        <v>264.6558677456342</v>
+      </c>
+      <c r="I71">
+        <v>16853.98799531602</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
       <c r="A72" s="2">
         <v>52047</v>
       </c>
       <c r="B72">
-        <v>4241165.366063904</v>
+        <v>6798.556286031379</v>
       </c>
       <c r="C72">
-        <v>227941.5620064282</v>
+        <v>885.7706489326429</v>
       </c>
       <c r="D72">
-        <v>5088105</v>
+        <v>53.38430742592993</v>
       </c>
       <c r="E72">
-        <v>-618998.0719296681</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
+        <v>7630.942627538092</v>
+      </c>
+      <c r="F72">
+        <v>16302.1579048129</v>
+      </c>
+      <c r="G72">
+        <v>460.4180648268868</v>
+      </c>
+      <c r="H72">
+        <v>258.7173694397407</v>
+      </c>
+      <c r="I72">
+        <v>16503.85860020004</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
       <c r="A73" s="2">
         <v>52139</v>
       </c>
       <c r="B73">
-        <v>3823487.986277678</v>
+        <v>6531.258778118937</v>
       </c>
       <c r="C73">
-        <v>205493.478485558</v>
+        <v>849.358080560072</v>
       </c>
       <c r="D73">
-        <v>5161140</v>
+        <v>51.19128921016495</v>
       </c>
       <c r="E73">
-        <v>-1132158.535236764</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
+        <v>7329.425569468844</v>
+      </c>
+      <c r="F73">
+        <v>15963.34374673181</v>
+      </c>
+      <c r="G73">
+        <v>456.7411804999085</v>
+      </c>
+      <c r="H73">
+        <v>252.895487217768</v>
+      </c>
+      <c r="I73">
+        <v>16167.18944001395</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
       <c r="A74" s="2">
         <v>52231</v>
       </c>
       <c r="B74">
-        <v>3446944.205049293</v>
+        <v>6272.765331046436</v>
       </c>
       <c r="C74">
-        <v>185256.121474256</v>
+        <v>814.3763295413362</v>
       </c>
       <c r="D74">
-        <v>5234175</v>
+        <v>49.08423235965327</v>
       </c>
       <c r="E74">
-        <v>-1601974.673476451</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
+        <v>7038.05742822812</v>
+      </c>
+      <c r="F74">
+        <v>15637.50406388215</v>
+      </c>
+      <c r="G74">
+        <v>452.9304249838281</v>
+      </c>
+      <c r="H74">
+        <v>247.1871852922294</v>
+      </c>
+      <c r="I74">
+        <v>15843.24730357375</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
       <c r="A75" s="2">
         <v>52321</v>
       </c>
       <c r="B75">
-        <v>3414662.233344416</v>
+        <v>6763.018478828446</v>
       </c>
       <c r="C75">
-        <v>165679.0154598426</v>
+        <v>777.6224706229152</v>
       </c>
       <c r="D75">
-        <v>5307210</v>
+        <v>46.96566625292827</v>
       </c>
       <c r="E75">
-        <v>-1726868.751195741</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
+        <v>7493.675283198432</v>
+      </c>
+      <c r="F75">
+        <v>15509.77600949793</v>
+      </c>
+      <c r="G75">
+        <v>320.0520333323113</v>
+      </c>
+      <c r="H75">
+        <v>243.411877911404</v>
+      </c>
+      <c r="I75">
+        <v>15586.41616491884</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9">
       <c r="A76" s="2">
         <v>52412</v>
       </c>
       <c r="B76">
-        <v>3041154.418098587</v>
+        <v>6454.544148461324</v>
       </c>
       <c r="C76">
-        <v>147556.4595911538</v>
+        <v>740.9402162280192</v>
       </c>
       <c r="D76">
-        <v>5380245</v>
+        <v>44.7515060297036</v>
       </c>
       <c r="E76">
-        <v>-2191534.12231026</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
+        <v>7150.73285865964</v>
+      </c>
+      <c r="F76">
+        <v>15171.61558406466</v>
+      </c>
+      <c r="G76">
+        <v>252.572503273135</v>
+      </c>
+      <c r="H76">
+        <v>241.5703761679807</v>
+      </c>
+      <c r="I76">
+        <v>15182.61771116981</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
       <c r="A77" s="2">
         <v>52504</v>
       </c>
       <c r="B77">
-        <v>2708502.206867528</v>
+        <v>6158.48483531086</v>
       </c>
       <c r="C77">
-        <v>131416.2128899972</v>
+        <v>705.932166645414</v>
       </c>
       <c r="D77">
-        <v>5453280</v>
+        <v>42.63819369501155</v>
       </c>
       <c r="E77">
-        <v>-2613361.580242475</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
+        <v>6821.778808261262</v>
+      </c>
+      <c r="F77">
+        <v>14843.65999401429</v>
+      </c>
+      <c r="G77">
+        <v>249.6327472838544</v>
+      </c>
+      <c r="H77">
+        <v>236.156521788631</v>
+      </c>
+      <c r="I77">
+        <v>14857.13621950952</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9">
       <c r="A78" s="2">
         <v>52596</v>
       </c>
       <c r="B78">
-        <v>2412236.669387189</v>
+        <v>5874.573239559386</v>
       </c>
       <c r="C78">
-        <v>117041.4433783584</v>
+        <v>672.5310701944354</v>
       </c>
       <c r="D78">
-        <v>5526315</v>
+        <v>40.62170718241838</v>
       </c>
       <c r="E78">
-        <v>-2997036.887234453</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
+        <v>6506.482602571403</v>
+      </c>
+      <c r="F78">
+        <v>14525.81518595418</v>
+      </c>
+      <c r="G78">
+        <v>246.6101654550448</v>
+      </c>
+      <c r="H78">
+        <v>230.8477725909967</v>
+      </c>
+      <c r="I78">
+        <v>14541.57757881823</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9">
       <c r="A79" s="2">
         <v>52687</v>
       </c>
       <c r="B79">
-        <v>2357270.826156529</v>
+        <v>6242.253529798396</v>
       </c>
       <c r="C79">
-        <v>103330.0365511742</v>
+        <v>637.9381251307249</v>
       </c>
       <c r="D79">
-        <v>5599350</v>
+        <v>38.61598188037179</v>
       </c>
       <c r="E79">
-        <v>-3138749.137292297</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
+        <v>6841.575673048748</v>
+      </c>
+      <c r="F79">
+        <v>14298.45768467742</v>
+      </c>
+      <c r="G79">
+        <v>243.5146384624345</v>
+      </c>
+      <c r="H79">
+        <v>225.6419533720702</v>
+      </c>
+      <c r="I79">
+        <v>14316.33036976778</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
       <c r="A80" s="2">
         <v>52778</v>
       </c>
       <c r="B80">
-        <v>2071647.120703041</v>
+        <v>5914.73155720045</v>
       </c>
       <c r="C80">
-        <v>90809.83412177759</v>
+        <v>603.7696711460835</v>
       </c>
       <c r="D80">
-        <v>5672385</v>
+        <v>36.54853258854342</v>
       </c>
       <c r="E80">
-        <v>-3509928.045175182</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
+        <v>6481.95269575799</v>
+      </c>
+      <c r="F80">
+        <v>14153.34556828961</v>
+      </c>
+      <c r="G80">
+        <v>240.3766975269539</v>
+      </c>
+      <c r="H80">
+        <v>220.5460906545123</v>
+      </c>
+      <c r="I80">
+        <v>14173.17617516205</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
       <c r="A81" s="2">
         <v>52870</v>
       </c>
       <c r="B81">
-        <v>1820631.615636098</v>
+        <v>5603.102653119934</v>
       </c>
       <c r="C81">
-        <v>79806.66850089344</v>
+        <v>571.3964471920949</v>
       </c>
       <c r="D81">
-        <v>5745420</v>
+        <v>34.5895438695766</v>
       </c>
       <c r="E81">
-        <v>-3844981.715863009</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
+        <v>6139.909556442452</v>
+      </c>
+      <c r="F81">
+        <v>13835.2508593672</v>
+      </c>
+      <c r="G81">
+        <v>237.2037940869047</v>
+      </c>
+      <c r="H81">
+        <v>215.562570439314</v>
+      </c>
+      <c r="I81">
+        <v>13856.89208301479</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9">
       <c r="A82" s="2">
         <v>52962</v>
       </c>
       <c r="B82">
-        <v>1600030.935156958</v>
+        <v>5306.800129567446</v>
       </c>
       <c r="C82">
-        <v>70136.72471497323</v>
+        <v>540.7312234518914</v>
       </c>
       <c r="D82">
-        <v>5818455</v>
+        <v>32.73377134309814</v>
       </c>
       <c r="E82">
-        <v>-4148287.340128068</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
+        <v>5814.797581676239</v>
+      </c>
+      <c r="F82">
+        <v>13514.01668227414</v>
+      </c>
+      <c r="G82">
+        <v>20.22701425469899</v>
+      </c>
+      <c r="H82">
+        <v>215.1805296745127</v>
+      </c>
+      <c r="I82">
+        <v>13319.06316685433</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
       <c r="A83" s="2">
         <v>53052</v>
       </c>
       <c r="B83">
-        <v>10660265.20538539</v>
+        <v>5583.834866379918</v>
       </c>
       <c r="C83">
-        <v>0</v>
+        <v>509.2995435040153</v>
       </c>
       <c r="D83">
-        <v>5891490</v>
+        <v>30.9042079491011</v>
       </c>
       <c r="E83">
-        <v>4768775.205385389</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
+        <v>6062.230201934832</v>
+      </c>
+      <c r="F83">
+        <v>13174.67628291309</v>
+      </c>
+      <c r="G83">
+        <v>19.33691621914478</v>
+      </c>
+      <c r="H83">
+        <v>212.6693171768345</v>
+      </c>
+      <c r="I83">
+        <v>12981.3438819554</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9">
       <c r="A84" s="2">
         <v>53143</v>
       </c>
       <c r="B84">
-        <v>0</v>
+        <v>5250.069197830805</v>
       </c>
       <c r="C84">
-        <v>0</v>
+        <v>478.5298614675438</v>
       </c>
       <c r="D84">
-        <v>5964525</v>
+        <v>29.03755717508331</v>
       </c>
       <c r="E84">
-        <v>-5964525</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
+        <v>5699.561502123266</v>
+      </c>
+      <c r="F84">
+        <v>12835.08996143773</v>
+      </c>
+      <c r="G84">
+        <v>18.4891942716791</v>
+      </c>
+      <c r="H84">
+        <v>208.0171501313374</v>
+      </c>
+      <c r="I84">
+        <v>12645.56200557807</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9">
       <c r="A85" s="2">
         <v>53235</v>
       </c>
       <c r="B85">
-        <v>0</v>
+        <v>4935.350497744364</v>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>449.6022573850016</v>
       </c>
       <c r="D85">
-        <v>6037560</v>
+        <v>27.28253973163991</v>
       </c>
       <c r="E85">
-        <v>-6037560</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
+        <v>5357.670215397725</v>
+      </c>
+      <c r="F85">
+        <v>12506.77632550249</v>
+      </c>
+      <c r="G85">
+        <v>17.68285321718337</v>
+      </c>
+      <c r="H85">
+        <v>203.4668095288924</v>
+      </c>
+      <c r="I85">
+        <v>12320.99236919078</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9">
       <c r="A86" s="2">
         <v>53327</v>
       </c>
       <c r="B86">
-        <v>0</v>
+        <v>4638.757154274069</v>
       </c>
       <c r="C86">
-        <v>0</v>
+        <v>422.4113560608313</v>
       </c>
       <c r="D86">
-        <v>6110595</v>
+        <v>25.63279068216778</v>
       </c>
       <c r="E86">
-        <v>-6110595</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5">
+        <v>5035.535719652733</v>
+      </c>
+      <c r="F86">
+        <v>12450.10885407795</v>
+      </c>
+      <c r="G86">
+        <v>16.91569176245073</v>
+      </c>
+      <c r="H86">
+        <v>199.0141298360448</v>
+      </c>
+      <c r="I86">
+        <v>12268.01041600436</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9">
       <c r="A87" s="2">
         <v>53417</v>
       </c>
       <c r="B87">
-        <v>0</v>
+        <v>5519.349966134115</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>390.2284548410477</v>
       </c>
       <c r="D87">
-        <v>6183630</v>
+        <v>23.83411759673596</v>
       </c>
       <c r="E87">
-        <v>-6183630</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5">
+        <v>5885.744303378427</v>
+      </c>
+      <c r="F87">
+        <v>12270.88650372555</v>
+      </c>
+      <c r="G87">
+        <v>16.18523501412183</v>
+      </c>
+      <c r="H87">
+        <v>194.6555176616689</v>
+      </c>
+      <c r="I87">
+        <v>12092.416221078</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9">
       <c r="A88" s="2">
         <v>53508</v>
       </c>
       <c r="B88">
-        <v>0</v>
+        <v>4401.05158196824</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>364.1508016357431</v>
       </c>
       <c r="D88">
-        <v>6256665</v>
+        <v>22.14768144760562</v>
       </c>
       <c r="E88">
-        <v>-6256665</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5">
+        <v>4743.054702156378</v>
+      </c>
+      <c r="F88">
+        <v>11960.466942861</v>
+      </c>
+      <c r="G88">
+        <v>15.48773682465648</v>
+      </c>
+      <c r="H88">
+        <v>190.3921362784477</v>
+      </c>
+      <c r="I88">
+        <v>11785.5625434072</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9">
       <c r="A89" s="2">
         <v>53600</v>
       </c>
       <c r="B89">
-        <v>0</v>
+        <v>4110.887546804313</v>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>339.7882918074505</v>
       </c>
       <c r="D89">
-        <v>6329700</v>
+        <v>20.66648614344285</v>
       </c>
       <c r="E89">
-        <v>-6329700</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5">
+        <v>4430.009352468321</v>
+      </c>
+      <c r="F89">
+        <v>11659.4931422073</v>
+      </c>
+      <c r="G89">
+        <v>14.82125484685294</v>
+      </c>
+      <c r="H89">
+        <v>186.2232640668235</v>
+      </c>
+      <c r="I89">
+        <v>11488.09113298733</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9">
       <c r="A90" s="2">
         <v>53692</v>
       </c>
       <c r="B90">
-        <v>0</v>
+        <v>3838.904565247219</v>
       </c>
       <c r="C90">
-        <v>0</v>
+        <v>317.0343956642155</v>
       </c>
       <c r="D90">
-        <v>6402735</v>
+        <v>19.28296931476167</v>
       </c>
       <c r="E90">
-        <v>-6402735</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5">
+        <v>4136.655991596674</v>
+      </c>
+      <c r="F90">
+        <v>11367.44876692172</v>
+      </c>
+      <c r="G90">
+        <v>14.18434893590765</v>
+      </c>
+      <c r="H90">
+        <v>182.1452602919782</v>
+      </c>
+      <c r="I90">
+        <v>11199.48785556565</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9">
       <c r="A91" s="2">
         <v>53782</v>
       </c>
       <c r="B91">
-        <v>0</v>
+        <v>3956.853723476778</v>
       </c>
       <c r="C91">
-        <v>0</v>
+        <v>294.1876533133718</v>
       </c>
       <c r="D91">
-        <v>6475770</v>
+        <v>17.9426873546542</v>
       </c>
       <c r="E91">
-        <v>-6475770</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5">
+        <v>4233.098689435496</v>
+      </c>
+      <c r="F91">
+        <v>11083.56216417924</v>
+      </c>
+      <c r="G91">
+        <v>13.57573019862786</v>
+      </c>
+      <c r="H91">
+        <v>178.1547836129649</v>
+      </c>
+      <c r="I91">
+        <v>10918.98311076491</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9">
       <c r="A92" s="2">
         <v>53873</v>
       </c>
       <c r="B92">
-        <v>0</v>
+        <v>3663.594395560826</v>
       </c>
       <c r="C92">
-        <v>0</v>
+        <v>272.2155990989855</v>
       </c>
       <c r="D92">
-        <v>6548805</v>
+        <v>16.60288152497671</v>
       </c>
       <c r="E92">
-        <v>-6548805</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5">
+        <v>3919.207113134835</v>
+      </c>
+      <c r="F92">
+        <v>10807.38185338582</v>
+      </c>
+      <c r="G92">
+        <v>12.99445492426887</v>
+      </c>
+      <c r="H92">
+        <v>174.249920183665</v>
+      </c>
+      <c r="I92">
+        <v>10646.12638812643</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9">
       <c r="A93" s="2">
         <v>53965</v>
       </c>
       <c r="B93">
-        <v>0</v>
+        <v>3391.397196138189</v>
       </c>
       <c r="C93">
-        <v>0</v>
+        <v>251.8742954851731</v>
       </c>
       <c r="D93">
-        <v>6621840</v>
+        <v>15.36242723137315</v>
       </c>
       <c r="E93">
-        <v>-6621840</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5">
+        <v>3627.909064391989</v>
+      </c>
+      <c r="F93">
+        <v>10539.23869975396</v>
+      </c>
+      <c r="G93">
+        <v>12.43930448790295</v>
+      </c>
+      <c r="H93">
+        <v>170.4281884110047</v>
+      </c>
+      <c r="I93">
+        <v>10381.24981583086</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9">
       <c r="A94" s="2">
         <v>54057</v>
       </c>
       <c r="B94">
-        <v>0</v>
+        <v>3138.893884367906</v>
       </c>
       <c r="C94">
-        <v>0</v>
+        <v>233.0462941337414</v>
       </c>
       <c r="D94">
-        <v>6694875</v>
+        <v>14.21418765828599</v>
       </c>
       <c r="E94">
-        <v>-6694875</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5">
+        <v>3357.725990843362</v>
+      </c>
+      <c r="F94">
+        <v>10278.65618865165</v>
+      </c>
+      <c r="G94">
+        <v>11.90904099365298</v>
+      </c>
+      <c r="H94">
+        <v>166.686386853288</v>
+      </c>
+      <c r="I94">
+        <v>10123.87884279202</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9">
       <c r="A95" s="2">
         <v>54148</v>
       </c>
       <c r="B95">
-        <v>0</v>
+        <v>3202.250902055529</v>
       </c>
       <c r="C95">
-        <v>0</v>
+        <v>214.3418105802694</v>
       </c>
       <c r="D95">
-        <v>6767910</v>
+        <v>13.11275638759132</v>
       </c>
       <c r="E95">
-        <v>-6767910</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5">
+        <v>3403.479956248207</v>
+      </c>
+      <c r="F95">
+        <v>10037.8765288516</v>
+      </c>
+      <c r="G95">
+        <v>11.40254814859258</v>
+      </c>
+      <c r="H95">
+        <v>163.0209485130008</v>
+      </c>
+      <c r="I95">
+        <v>9886.258128487194</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9">
       <c r="A96" s="2">
         <v>54239</v>
       </c>
       <c r="B96">
-        <v>0</v>
+        <v>2936.49936714441</v>
       </c>
       <c r="C96">
-        <v>0</v>
+        <v>196.5343603088232</v>
       </c>
       <c r="D96">
-        <v>6840945</v>
+        <v>12.02338901524208</v>
       </c>
       <c r="E96">
-        <v>-6840945</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5">
+        <v>3121.010338437991</v>
+      </c>
+      <c r="F96">
+        <v>9827.785796873715</v>
+      </c>
+      <c r="G96">
+        <v>10.91897417017701</v>
+      </c>
+      <c r="H96">
+        <v>159.4198945875147</v>
+      </c>
+      <c r="I96">
+        <v>9679.284876456377</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9">
       <c r="A97" s="2">
         <v>54331</v>
       </c>
       <c r="B97">
-        <v>0</v>
+        <v>2692.484144331052</v>
       </c>
       <c r="C97">
-        <v>0</v>
+        <v>180.2063654751494</v>
       </c>
       <c r="D97">
-        <v>6913980</v>
+        <v>11.02448423305124</v>
       </c>
       <c r="E97">
-        <v>-6913980</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5">
+        <v>2861.666025573151</v>
+      </c>
+      <c r="F97">
+        <v>9621.485146476021</v>
+      </c>
+      <c r="G97">
+        <v>10.45727307978419</v>
+      </c>
+      <c r="H97">
+        <v>155.8751993257386</v>
+      </c>
+      <c r="I97">
+        <v>9476.067220230067</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9">
       <c r="A98" s="2">
         <v>54423</v>
       </c>
       <c r="B98">
-        <v>0</v>
+        <v>2468.514974146668</v>
       </c>
       <c r="C98">
-        <v>0</v>
+        <v>165.236551850229</v>
       </c>
       <c r="D98">
-        <v>6987015</v>
+        <v>10.10863806200685</v>
       </c>
       <c r="E98">
-        <v>-6987015</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5">
+        <v>2623.64288793489</v>
+      </c>
+      <c r="F98">
+        <v>9418.570523688135</v>
+      </c>
+      <c r="G98">
+        <v>10.01639293133507</v>
+      </c>
+      <c r="H98">
+        <v>152.3849555075461</v>
+      </c>
+      <c r="I98">
+        <v>9276.201961111923</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9">
       <c r="A99" s="2">
         <v>54513</v>
       </c>
       <c r="B99">
-        <v>0</v>
+        <v>2494.043213785615</v>
       </c>
       <c r="C99">
-        <v>0</v>
+        <v>150.5167688128427</v>
       </c>
       <c r="D99">
-        <v>7060050</v>
+        <v>9.238808220638639</v>
       </c>
       <c r="E99">
-        <v>-7060050</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5">
+        <v>2635.321174377818</v>
+      </c>
+      <c r="F99">
+        <v>9206.114452574289</v>
+      </c>
+      <c r="G99">
+        <v>9.595379273991368</v>
+      </c>
+      <c r="H99">
+        <v>148.9481888482051</v>
+      </c>
+      <c r="I99">
+        <v>9066.761643000076</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9">
       <c r="A100" s="2">
         <v>54604</v>
       </c>
       <c r="B100">
-        <v>0</v>
+        <v>2263.505839240609</v>
       </c>
       <c r="C100">
-        <v>0</v>
+        <v>136.6469173707343</v>
       </c>
       <c r="D100">
-        <v>7133085</v>
+        <v>8.387379074149639</v>
       </c>
       <c r="E100">
-        <v>-7133085</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5">
+        <v>2391.765377537194</v>
+      </c>
+      <c r="F100">
+        <v>8973.162237096094</v>
+      </c>
+      <c r="G100">
+        <v>9.193480090236793</v>
+      </c>
+      <c r="H100">
+        <v>145.5743166819568</v>
+      </c>
+      <c r="I100">
+        <v>8836.781400504375</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9">
       <c r="A101" s="2">
         <v>54696</v>
       </c>
       <c r="B101">
-        <v>0</v>
+        <v>2054.189203950904</v>
       </c>
       <c r="C101">
-        <v>0</v>
+        <v>124.0600789299995</v>
       </c>
       <c r="D101">
-        <v>7206120</v>
+        <v>7.614697196567411</v>
       </c>
       <c r="E101">
-        <v>-7206120</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5">
+        <v>2170.634585684336</v>
+      </c>
+      <c r="F101">
+        <v>8746.035537744534</v>
+      </c>
+      <c r="G101">
+        <v>8.809807594187106</v>
+      </c>
+      <c r="H101">
+        <v>142.2680215119538</v>
+      </c>
+      <c r="I101">
+        <v>8612.577323826767</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9">
       <c r="A102" s="2">
         <v>54788</v>
       </c>
       <c r="B102">
-        <v>0</v>
+        <v>1864.184530228753</v>
       </c>
       <c r="C102">
-        <v>0</v>
+        <v>112.6379716360049</v>
       </c>
       <c r="D102">
-        <v>7279155</v>
+        <v>6.913508769904189</v>
       </c>
       <c r="E102">
-        <v>-7279155</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5">
+        <v>1969.908993094854</v>
+      </c>
+      <c r="F102">
+        <v>8524.364585991514</v>
+      </c>
+      <c r="G102">
+        <v>8.443476245886597</v>
+      </c>
+      <c r="H102">
+        <v>139.0270799461302</v>
+      </c>
+      <c r="I102">
+        <v>8393.780982291271</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9">
       <c r="A103" s="2">
         <v>54878</v>
       </c>
       <c r="B103">
-        <v>0</v>
+        <v>1863.106659377362</v>
       </c>
       <c r="C103">
-        <v>0</v>
+        <v>101.5321573161133</v>
       </c>
       <c r="D103">
-        <v>7352190</v>
+        <v>6.254695326607647</v>
       </c>
       <c r="E103">
-        <v>-7352190</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5">
+        <v>1958.384121366868</v>
+      </c>
+      <c r="F103">
+        <v>8321.828703390511</v>
+      </c>
+      <c r="G103">
+        <v>8.093678392248691</v>
+      </c>
+      <c r="H103">
+        <v>135.8468452850898</v>
+      </c>
+      <c r="I103">
+        <v>8194.07553649767</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9">
       <c r="A104" s="2">
         <v>54969</v>
       </c>
       <c r="B104">
-        <v>0</v>
+        <v>1672.174131697098</v>
       </c>
       <c r="C104">
-        <v>0</v>
+        <v>91.18403518185357</v>
       </c>
       <c r="D104">
-        <v>7425225</v>
+        <v>5.617088287757246</v>
       </c>
       <c r="E104">
-        <v>-7425225</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5">
+        <v>1757.741078591194</v>
+      </c>
+      <c r="F104">
+        <v>8112.127470320338</v>
+      </c>
+      <c r="G104">
+        <v>7.75976094370659</v>
+      </c>
+      <c r="H104">
+        <v>132.6919896390618</v>
+      </c>
+      <c r="I104">
+        <v>7987.195241624982</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9">
       <c r="A105" s="2">
         <v>55061</v>
       </c>
       <c r="B105">
-        <v>0</v>
+        <v>1500.843681762967</v>
       </c>
       <c r="C105">
-        <v>0</v>
+        <v>81.89681391464461</v>
       </c>
       <c r="D105">
-        <v>7498260</v>
+        <v>5.044852857193066</v>
       </c>
       <c r="E105">
-        <v>-7498260</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5">
+        <v>1577.695642820418</v>
+      </c>
+      <c r="F105">
+        <v>7841.602839579356</v>
+      </c>
+      <c r="G105">
+        <v>7.440977170627258</v>
+      </c>
+      <c r="H105">
+        <v>129.6058979351604</v>
+      </c>
+      <c r="I105">
+        <v>7719.437918814823</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9">
       <c r="A106" s="2">
         <v>55153</v>
       </c>
       <c r="B106">
-        <v>0</v>
+        <v>1347.118536013157</v>
       </c>
       <c r="C106">
-        <v>0</v>
+        <v>73.56147582382189</v>
       </c>
       <c r="D106">
-        <v>7571295</v>
+        <v>4.531273669053867</v>
       </c>
       <c r="E106">
-        <v>-7571295</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5">
+        <v>1416.148738167925</v>
+      </c>
+      <c r="F106">
+        <v>7593.378110126447</v>
+      </c>
+      <c r="G106">
+        <v>7.136587347703007</v>
+      </c>
+      <c r="H106">
+        <v>126.6347069430069</v>
+      </c>
+      <c r="I106">
+        <v>7473.879990531143</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9">
       <c r="A107" s="2">
         <v>55243</v>
       </c>
       <c r="B107">
-        <v>0</v>
+        <v>2406.01313665655</v>
       </c>
       <c r="C107">
-        <v>0</v>
+        <v>58.37325843994768</v>
       </c>
       <c r="D107">
-        <v>7644330</v>
+        <v>3.762832082790758</v>
       </c>
       <c r="E107">
-        <v>-7644330</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5">
+        <v>2460.623563013707</v>
+      </c>
+      <c r="F107">
+        <v>7391.506860884838</v>
+      </c>
+      <c r="G107">
+        <v>6.845913848923645</v>
+      </c>
+      <c r="H107">
+        <v>123.7443856621028</v>
+      </c>
+      <c r="I107">
+        <v>7274.608389071658</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9">
       <c r="A108" s="2">
         <v>55334</v>
       </c>
       <c r="B108">
-        <v>0</v>
+        <v>1024.852638247331</v>
       </c>
       <c r="C108">
-        <v>0</v>
+        <v>51.99080947368914</v>
       </c>
       <c r="D108">
-        <v>7717365</v>
+        <v>3.211648074396041</v>
       </c>
       <c r="E108">
-        <v>-7717365</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5">
+        <v>1073.631799646624</v>
+      </c>
+      <c r="F108">
+        <v>7212.104247597021</v>
+      </c>
+      <c r="G108">
+        <v>6.56839711809935</v>
+      </c>
+      <c r="H108">
+        <v>120.8484765126137</v>
+      </c>
+      <c r="I108">
+        <v>7097.824168202507</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9">
       <c r="A109" s="2">
         <v>55426</v>
       </c>
       <c r="B109">
-        <v>0</v>
+        <v>912.5450517710865</v>
       </c>
       <c r="C109">
-        <v>0</v>
+        <v>46.30802937084542</v>
       </c>
       <c r="D109">
-        <v>7790400</v>
+        <v>2.860567590594455</v>
       </c>
       <c r="E109">
-        <v>-7790400</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5">
+        <v>955.9925135513374</v>
+      </c>
+      <c r="F109">
+        <v>6995.115192225974</v>
+      </c>
+      <c r="G109">
+        <v>6.303413651414983</v>
+      </c>
+      <c r="H109">
+        <v>117.9996652519319</v>
+      </c>
+      <c r="I109">
+        <v>6883.418940625457</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9">
       <c r="A110" s="2">
         <v>55518</v>
       </c>
       <c r="B110">
-        <v>0</v>
+        <v>812.5772263126621</v>
       </c>
       <c r="C110">
-        <v>0</v>
+        <v>41.24801389766988</v>
       </c>
       <c r="D110">
-        <v>7863435</v>
+        <v>2.547965346845592</v>
       </c>
       <c r="E110">
-        <v>-7863435</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5">
+        <v>851.2772748634865</v>
+      </c>
+      <c r="F110">
+        <v>6792.705489370974</v>
+      </c>
+      <c r="G110">
+        <v>6.050349288991161</v>
+      </c>
+      <c r="H110">
+        <v>115.2682545750428</v>
+      </c>
+      <c r="I110">
+        <v>6683.487584084922</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9">
       <c r="A111" s="2">
         <v>55609</v>
       </c>
       <c r="B111">
-        <v>0</v>
+        <v>794.4014181989288</v>
       </c>
       <c r="C111">
-        <v>0</v>
+        <v>36.4348007889101</v>
       </c>
       <c r="D111">
-        <v>7936470</v>
+        <v>2.260224794874751</v>
       </c>
       <c r="E111">
-        <v>-7936470</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5">
+        <v>828.5759941929641</v>
+      </c>
+      <c r="F111">
+        <v>6608.868698041545</v>
+      </c>
+      <c r="G111">
+        <v>5.808639410639724</v>
+      </c>
+      <c r="H111">
+        <v>112.613331036139</v>
+      </c>
+      <c r="I111">
+        <v>6502.064006416045</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9">
       <c r="A112" s="2">
         <v>55700</v>
       </c>
       <c r="B112">
-        <v>0</v>
+        <v>698.4421063528694</v>
       </c>
       <c r="C112">
-        <v>0</v>
+        <v>32.04410375911694</v>
       </c>
       <c r="D112">
-        <v>8009505</v>
+        <v>1.987820462023487</v>
       </c>
       <c r="E112">
-        <v>-8009505</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5">
+        <v>728.4983896499629</v>
+      </c>
+      <c r="F112">
+        <v>6434.1286904315</v>
+      </c>
+      <c r="G112">
+        <v>5.577810038306772</v>
+      </c>
+      <c r="H112">
+        <v>110.0111530594967</v>
+      </c>
+      <c r="I112">
+        <v>6329.69534741031</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9">
       <c r="A113" s="2">
         <v>55792</v>
       </c>
       <c r="B113">
-        <v>0</v>
+        <v>614.1021560585948</v>
       </c>
       <c r="C113">
-        <v>0</v>
+        <v>28.1837749927193</v>
       </c>
       <c r="D113">
-        <v>8082540</v>
+        <v>1.748324350192585</v>
       </c>
       <c r="E113">
-        <v>-8082540</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5">
+        <v>640.5376067011215</v>
+      </c>
+      <c r="F113">
+        <v>6263.526164005573</v>
+      </c>
+      <c r="G113">
+        <v>5.357343536167785</v>
+      </c>
+      <c r="H113">
+        <v>107.4579639801371</v>
+      </c>
+      <c r="I113">
+        <v>6161.425543561604</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9">
       <c r="A114" s="2">
         <v>55884</v>
       </c>
       <c r="B114">
-        <v>0</v>
+        <v>539.971169295622</v>
       </c>
       <c r="C114">
-        <v>0</v>
+        <v>24.78959459960642</v>
       </c>
       <c r="D114">
-        <v>8155575</v>
+        <v>1.537751319222096</v>
       </c>
       <c r="E114">
-        <v>-8155575</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5">
+        <v>563.2230125760063</v>
+      </c>
+      <c r="F114">
+        <v>6096.905969030248</v>
+      </c>
+      <c r="G114">
+        <v>5.146732308283324</v>
+      </c>
+      <c r="H114">
+        <v>104.952512161131</v>
+      </c>
+      <c r="I114">
+        <v>5997.100189177401</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9">
       <c r="A115" s="2">
         <v>55974</v>
       </c>
       <c r="B115">
-        <v>0</v>
+        <v>1652.299111455083</v>
       </c>
       <c r="C115">
-        <v>0</v>
+        <v>14.03792317638426</v>
       </c>
       <c r="D115">
-        <v>8228610</v>
+        <v>1.039117590140449</v>
       </c>
       <c r="E115">
-        <v>-8228610</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5">
+        <v>1665.297917041327</v>
+      </c>
+      <c r="F115">
+        <v>5930.142227603363</v>
+      </c>
+      <c r="G115">
+        <v>4.945825936596404</v>
+      </c>
+      <c r="H115">
+        <v>102.4938799308621</v>
+      </c>
+      <c r="I115">
+        <v>5832.594173609097</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9">
       <c r="A116" s="2">
         <v>56065</v>
       </c>
       <c r="B116">
-        <v>0</v>
+        <v>284.2006274466374</v>
       </c>
       <c r="C116">
-        <v>0</v>
+        <v>12.24366488885914</v>
       </c>
       <c r="D116">
-        <v>8301645</v>
+        <v>0.7616889738028653</v>
       </c>
       <c r="E116">
-        <v>-8301645</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5">
+        <v>295.6826033616936</v>
+      </c>
+      <c r="F116">
+        <v>5759.758490080752</v>
+      </c>
+      <c r="G116">
+        <v>4.755647721008676</v>
+      </c>
+      <c r="H116">
+        <v>100.0848339945495</v>
+      </c>
+      <c r="I116">
+        <v>5664.429303807211</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9">
       <c r="A117" s="2">
         <v>56157</v>
       </c>
       <c r="B117">
-        <v>0</v>
+        <v>247.8755012361012</v>
       </c>
       <c r="C117">
-        <v>0</v>
+        <v>10.67873986964599</v>
       </c>
       <c r="D117">
-        <v>8374680</v>
+        <v>0.6643336359376877</v>
       </c>
       <c r="E117">
-        <v>-8374680</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5">
+        <v>257.8899074698095</v>
+      </c>
+      <c r="F117">
+        <v>5594.032432559067</v>
+      </c>
+      <c r="G117">
+        <v>4.575886958530861</v>
+      </c>
+      <c r="H117">
+        <v>97.72647282629315</v>
+      </c>
+      <c r="I117">
+        <v>5500.881846691304</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9">
       <c r="A118" s="2">
         <v>56249</v>
       </c>
       <c r="B118">
-        <v>0</v>
+        <v>216.19327397363</v>
       </c>
       <c r="C118">
-        <v>0</v>
+        <v>9.313835868485015</v>
       </c>
       <c r="D118">
-        <v>8447715</v>
+        <v>0.5794217784651984</v>
       </c>
       <c r="E118">
-        <v>-8447715</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5">
+        <v>224.9276880636498</v>
+      </c>
+      <c r="F118">
+        <v>5432.734740277299</v>
+      </c>
+      <c r="G118">
+        <v>4.406002332051289</v>
+      </c>
+      <c r="H118">
+        <v>95.41745516611572</v>
+      </c>
+      <c r="I118">
+        <v>5341.723287443235</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9">
       <c r="A119" s="2">
         <v>56339</v>
       </c>
       <c r="B119">
-        <v>0</v>
+        <v>1409.511097392875</v>
       </c>
       <c r="C119">
         <v>0</v>
       </c>
       <c r="D119">
-        <v>8520750</v>
+        <v>0.1761888871741094</v>
       </c>
       <c r="E119">
-        <v>-8520750</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5">
+        <v>1409.334908505701</v>
+      </c>
+      <c r="F119">
+        <v>5302.322417337307</v>
+      </c>
+      <c r="G119">
+        <v>4.094989735340986</v>
+      </c>
+      <c r="H119">
+        <v>93.12659368758426</v>
+      </c>
+      <c r="I119">
+        <v>5213.290813385064</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9">
       <c r="A120" s="2">
         <v>56430</v>
       </c>
@@ -2427,13 +3870,25 @@
         <v>0</v>
       </c>
       <c r="D120">
-        <v>8593785</v>
+        <v>0</v>
       </c>
       <c r="E120">
-        <v>-8593785</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F120">
+        <v>5182.624698105475</v>
+      </c>
+      <c r="G120">
+        <v>3.940682507926912</v>
+      </c>
+      <c r="H120">
+        <v>90.89933329689364</v>
+      </c>
+      <c r="I120">
+        <v>5095.666047316508</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9">
       <c r="A121" s="2">
         <v>56522</v>
       </c>
@@ -2444,13 +3899,25 @@
         <v>0</v>
       </c>
       <c r="D121">
-        <v>8666820</v>
+        <v>0</v>
       </c>
       <c r="E121">
-        <v>-8666820</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F121">
+        <v>4989.451374362433</v>
+      </c>
+      <c r="G121">
+        <v>3.79309907517471</v>
+      </c>
+      <c r="H121">
+        <v>88.73570123357493</v>
+      </c>
+      <c r="I121">
+        <v>4904.508772204033</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9">
       <c r="A122" s="2">
         <v>56614</v>
       </c>
@@ -2461,13 +3928,25 @@
         <v>0</v>
       </c>
       <c r="D122">
-        <v>8739855</v>
+        <v>0</v>
       </c>
       <c r="E122">
-        <v>-8739855</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F122">
+        <v>4817.495987657387</v>
+      </c>
+      <c r="G122">
+        <v>3.651918110155948</v>
+      </c>
+      <c r="H122">
+        <v>86.61945037197505</v>
+      </c>
+      <c r="I122">
+        <v>4734.528455395567</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9">
       <c r="A123" s="2">
         <v>56704</v>
       </c>
@@ -2478,13 +3957,25 @@
         <v>0</v>
       </c>
       <c r="D123">
-        <v>8812890</v>
+        <v>0</v>
       </c>
       <c r="E123">
-        <v>-8812890</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F123">
+        <v>4669.558999786679</v>
+      </c>
+      <c r="G123">
+        <v>3.516841097981017</v>
+      </c>
+      <c r="H123">
+        <v>84.54950155840267</v>
+      </c>
+      <c r="I123">
+        <v>4588.526339326258</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9">
       <c r="A124" s="2">
         <v>56795</v>
       </c>
@@ -2495,13 +3986,25 @@
         <v>0</v>
       </c>
       <c r="D124">
-        <v>8885925</v>
+        <v>0</v>
       </c>
       <c r="E124">
-        <v>-8885925</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F124">
+        <v>4524.129594728313</v>
+      </c>
+      <c r="G124">
+        <v>3.387607205220999</v>
+      </c>
+      <c r="H124">
+        <v>82.52673843965766</v>
+      </c>
+      <c r="I124">
+        <v>4444.990463493877</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9">
       <c r="A125" s="2">
         <v>56887</v>
       </c>
@@ -2512,13 +4015,25 @@
         <v>0</v>
       </c>
       <c r="D125">
-        <v>8958960</v>
+        <v>0</v>
       </c>
       <c r="E125">
-        <v>-8958960</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F125">
+        <v>4383.150771040842</v>
+      </c>
+      <c r="G125">
+        <v>3.263944146972425</v>
+      </c>
+      <c r="H125">
+        <v>80.55117503550991</v>
+      </c>
+      <c r="I125">
+        <v>4305.863540152304</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9">
       <c r="A126" s="2">
         <v>56979</v>
       </c>
@@ -2529,13 +4044,25 @@
         <v>0</v>
       </c>
       <c r="D126">
-        <v>9031995</v>
+        <v>0</v>
       </c>
       <c r="E126">
-        <v>-9031995</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F126">
+        <v>4246.468520484095</v>
+      </c>
+      <c r="G126">
+        <v>3.145587340845765</v>
+      </c>
+      <c r="H126">
+        <v>78.62153634664395</v>
+      </c>
+      <c r="I126">
+        <v>4170.992571478298</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9">
       <c r="A127" s="2">
         <v>57070</v>
       </c>
@@ -2546,13 +4073,25 @@
         <v>0</v>
       </c>
       <c r="D127">
-        <v>9105030</v>
+        <v>0</v>
       </c>
       <c r="E127">
-        <v>-9105030</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F127">
+        <v>4112.471607823087</v>
+      </c>
+      <c r="G127">
+        <v>3.032290249044471</v>
+      </c>
+      <c r="H127">
+        <v>76.73670480979978</v>
+      </c>
+      <c r="I127">
+        <v>4038.767193262332</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9">
       <c r="A128" s="2">
         <v>57161</v>
       </c>
@@ -2563,13 +4102,25 @@
         <v>0</v>
       </c>
       <c r="D128">
-        <v>9178065</v>
+        <v>0</v>
       </c>
       <c r="E128">
-        <v>-9178065</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F128">
+        <v>3979.790461841333</v>
+      </c>
+      <c r="G128">
+        <v>2.923834889493785</v>
+      </c>
+      <c r="H128">
+        <v>74.8971716897282</v>
+      </c>
+      <c r="I128">
+        <v>3907.817125041098</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9">
       <c r="A129" s="2">
         <v>57253</v>
       </c>
@@ -2580,13 +4131,25 @@
         <v>0</v>
       </c>
       <c r="D129">
-        <v>9251100</v>
+        <v>0</v>
       </c>
       <c r="E129">
-        <v>-9251100</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F129">
+        <v>3851.407961914061</v>
+      </c>
+      <c r="G129">
+        <v>2.819996800203972</v>
+      </c>
+      <c r="H129">
+        <v>73.10271967131328</v>
+      </c>
+      <c r="I129">
+        <v>3781.125239042952</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9">
       <c r="A130" s="2">
         <v>57345</v>
       </c>
@@ -2597,13 +4160,25 @@
         <v>0</v>
       </c>
       <c r="D130">
-        <v>9324135</v>
+        <v>0</v>
       </c>
       <c r="E130">
-        <v>-9324135</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F130">
+        <v>3727.176024002935</v>
+      </c>
+      <c r="G130">
+        <v>2.720558529307381</v>
+      </c>
+      <c r="H130">
+        <v>71.35208227939455</v>
+      </c>
+      <c r="I130">
+        <v>3658.544500252848</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9">
       <c r="A131" s="2">
         <v>57435</v>
       </c>
@@ -2614,13 +4189,25 @@
         <v>0</v>
       </c>
       <c r="D131">
-        <v>9397170</v>
+        <v>0</v>
       </c>
       <c r="E131">
-        <v>-9397170</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F131">
+        <v>3605.800772009485</v>
+      </c>
+      <c r="G131">
+        <v>2.625316893462258</v>
+      </c>
+      <c r="H131">
+        <v>69.64412791497914</v>
+      </c>
+      <c r="I131">
+        <v>3538.781960987968</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9">
       <c r="A132" s="2">
         <v>57526</v>
       </c>
@@ -2631,13 +4218,25 @@
         <v>0</v>
       </c>
       <c r="D132">
-        <v>9470205</v>
+        <v>0</v>
       </c>
       <c r="E132">
-        <v>-9470205</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F132">
+        <v>3486.180830100217</v>
+      </c>
+      <c r="G132">
+        <v>2.534090371082629</v>
+      </c>
+      <c r="H132">
+        <v>67.97905212692218</v>
+      </c>
+      <c r="I132">
+        <v>3420.735868344377</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9">
       <c r="A133" s="2">
         <v>57618</v>
       </c>
@@ -2648,13 +4247,25 @@
         <v>0</v>
       </c>
       <c r="D133">
-        <v>9543240</v>
+        <v>0</v>
       </c>
       <c r="E133">
-        <v>-9543240</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F133">
+        <v>3370.624095746475</v>
+      </c>
+      <c r="G133">
+        <v>2.446694207419336</v>
+      </c>
+      <c r="H133">
+        <v>66.35647216522406</v>
+      </c>
+      <c r="I133">
+        <v>3306.714317788671</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9">
       <c r="A134" s="2">
         <v>57710</v>
       </c>
@@ -2665,13 +4276,25 @@
         <v>0</v>
       </c>
       <c r="D134">
-        <v>9616275</v>
+        <v>0</v>
       </c>
       <c r="E134">
-        <v>-9616275</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F134">
+        <v>3258.984672015649</v>
+      </c>
+      <c r="G134">
+        <v>2.36294986845824</v>
+      </c>
+      <c r="H134">
+        <v>64.77514868762546</v>
+      </c>
+      <c r="I134">
+        <v>3196.572473196482</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9">
       <c r="A135" s="2">
         <v>57800</v>
       </c>
@@ -2682,13 +4305,25 @@
         <v>0</v>
       </c>
       <c r="D135">
-        <v>9689310</v>
+        <v>0</v>
       </c>
       <c r="E135">
-        <v>-9689310</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F135">
+        <v>3145.835847491036</v>
+      </c>
+      <c r="G135">
+        <v>2.282690092023966</v>
+      </c>
+      <c r="H135">
+        <v>63.23492101104138</v>
+      </c>
+      <c r="I135">
+        <v>3084.883616572019</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9">
       <c r="A136" s="2">
         <v>57891</v>
       </c>
@@ -2699,13 +4334,25 @@
         <v>0</v>
       </c>
       <c r="D136">
-        <v>9762345</v>
+        <v>0</v>
       </c>
       <c r="E136">
-        <v>-9762345</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F136">
+        <v>3026.771168006707</v>
+      </c>
+      <c r="G136">
+        <v>2.205764023246917</v>
+      </c>
+      <c r="H136">
+        <v>61.75077600905156</v>
+      </c>
+      <c r="I136">
+        <v>2967.226156020903</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9">
       <c r="A137" s="2">
         <v>57983</v>
       </c>
@@ -2716,13 +4363,25 @@
         <v>0</v>
       </c>
       <c r="D137">
-        <v>9835380</v>
+        <v>0</v>
       </c>
       <c r="E137">
-        <v>-9835380</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F137">
+        <v>2912.668543836692</v>
+      </c>
+      <c r="G137">
+        <v>2.132019698982229</v>
+      </c>
+      <c r="H137">
+        <v>60.33048939919296</v>
+      </c>
+      <c r="I137">
+        <v>2854.470074136481</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9">
       <c r="A138" s="2">
         <v>58075</v>
       </c>
@@ -2733,13 +4392,25 @@
         <v>0</v>
       </c>
       <c r="D138">
-        <v>9908415</v>
+        <v>0</v>
       </c>
       <c r="E138">
-        <v>-9908415</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F138">
+        <v>2802.8922427917</v>
+      </c>
+      <c r="G138">
+        <v>2.061310592918274</v>
+      </c>
+      <c r="H138">
+        <v>58.97197735562919</v>
+      </c>
+      <c r="I138">
+        <v>2745.981576028989</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9">
       <c r="A139" s="2">
         <v>58165</v>
       </c>
@@ -2750,13 +4421,25 @@
         <v>0</v>
       </c>
       <c r="D139">
-        <v>9981450</v>
+        <v>0</v>
       </c>
       <c r="E139">
-        <v>-9981450</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F139">
+        <v>2964.665113867783</v>
+      </c>
+      <c r="G139">
+        <v>1.993499123328989</v>
+      </c>
+      <c r="H139">
+        <v>57.61149325949698</v>
+      </c>
+      <c r="I139">
+        <v>2909.047119731615</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9">
       <c r="A140" s="2">
         <v>58256</v>
       </c>
@@ -2767,13 +4450,25 @@
         <v>0</v>
       </c>
       <c r="D140">
-        <v>10054485</v>
+        <v>0</v>
       </c>
       <c r="E140">
-        <v>-10054485</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F140">
+        <v>3217.150706497341</v>
+      </c>
+      <c r="G140">
+        <v>1.928460273851466</v>
+      </c>
+      <c r="H140">
+        <v>55.42687319316931</v>
+      </c>
+      <c r="I140">
+        <v>3163.652293578023</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9">
       <c r="A141" s="2">
         <v>58348</v>
       </c>
@@ -2784,13 +4479,25 @@
         <v>0</v>
       </c>
       <c r="D141">
-        <v>10127520</v>
+        <v>0</v>
       </c>
       <c r="E141">
-        <v>-10127520</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F141">
+        <v>2739.134019088517</v>
+      </c>
+      <c r="G141">
+        <v>1.866069085344087</v>
+      </c>
+      <c r="H141">
+        <v>53.16207268302389</v>
+      </c>
+      <c r="I141">
+        <v>2687.838015490836</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9">
       <c r="A142" s="2">
         <v>58440</v>
       </c>
@@ -2801,13 +4508,25 @@
         <v>0</v>
       </c>
       <c r="D142">
-        <v>10200555</v>
+        <v>0</v>
       </c>
       <c r="E142">
-        <v>-10200555</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F142">
+        <v>2426.775881726855</v>
+      </c>
+      <c r="G142">
+        <v>1.806205253951727</v>
+      </c>
+      <c r="H142">
+        <v>51.73291092564348</v>
+      </c>
+      <c r="I142">
+        <v>2376.849176055163</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9">
       <c r="A143" s="2">
         <v>58531</v>
       </c>
@@ -2818,13 +4537,25 @@
         <v>0</v>
       </c>
       <c r="D143">
-        <v>10273590</v>
+        <v>0</v>
       </c>
       <c r="E143">
-        <v>-10273590</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F143">
+        <v>2463.473471917801</v>
+      </c>
+      <c r="G143">
+        <v>1.748755624853464</v>
+      </c>
+      <c r="H143">
+        <v>50.55648401009505</v>
+      </c>
+      <c r="I143">
+        <v>2414.66574353256</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9">
       <c r="A144" s="2">
         <v>58622</v>
       </c>
@@ -2835,13 +4566,25 @@
         <v>0</v>
       </c>
       <c r="D144">
-        <v>10346625</v>
+        <v>0</v>
       </c>
       <c r="E144">
-        <v>-10346625</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F144">
+        <v>2553.281533755954</v>
+      </c>
+      <c r="G144">
+        <v>1.693616838504207</v>
+      </c>
+      <c r="H144">
+        <v>48.23531276991889</v>
+      </c>
+      <c r="I144">
+        <v>2506.739837824539</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9">
       <c r="A145" s="2">
         <v>58714</v>
       </c>
@@ -2852,13 +4595,25 @@
         <v>0</v>
       </c>
       <c r="D145">
-        <v>10419660</v>
+        <v>0</v>
       </c>
       <c r="E145">
-        <v>-10419660</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F145">
+        <v>2232.228358024061</v>
+      </c>
+      <c r="G145">
+        <v>1.640686102238446</v>
+      </c>
+      <c r="H145">
+        <v>45.76824065085489</v>
+      </c>
+      <c r="I145">
+        <v>2188.100803475444</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9">
       <c r="A146" s="2">
         <v>58806</v>
       </c>
@@ -2869,13 +4624,25 @@
         <v>0</v>
       </c>
       <c r="D146">
-        <v>10492695</v>
+        <v>0</v>
       </c>
       <c r="E146">
-        <v>-10492695</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F146">
+        <v>2007.470362398591</v>
+      </c>
+      <c r="G146">
+        <v>1.589864535245744</v>
+      </c>
+      <c r="H146">
+        <v>44.41137967809398</v>
+      </c>
+      <c r="I146">
+        <v>1964.648847255743</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9">
       <c r="A147" s="2">
         <v>58896</v>
       </c>
@@ -2886,13 +4653,25 @@
         <v>0</v>
       </c>
       <c r="D147">
-        <v>10565730</v>
+        <v>0</v>
       </c>
       <c r="E147">
-        <v>-10565730</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F147">
+        <v>2609.627808302586</v>
+      </c>
+      <c r="G147">
+        <v>1.541059068287602</v>
+      </c>
+      <c r="H147">
+        <v>43.41110636354956</v>
+      </c>
+      <c r="I147">
+        <v>2567.757761007324</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9">
       <c r="A148" s="2">
         <v>58987</v>
       </c>
@@ -2903,13 +4682,25 @@
         <v>0</v>
       </c>
       <c r="D148">
-        <v>10638765</v>
+        <v>0</v>
       </c>
       <c r="E148">
-        <v>-10638765</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F148">
+        <v>3465.305921500222</v>
+      </c>
+      <c r="G148">
+        <v>1.494184603547866</v>
+      </c>
+      <c r="H148">
+        <v>41.45875947701575</v>
+      </c>
+      <c r="I148">
+        <v>3425.341346626755</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9">
       <c r="A149" s="2">
         <v>59079</v>
       </c>
@@ -2920,13 +4711,25 @@
         <v>0</v>
       </c>
       <c r="D149">
-        <v>10711800</v>
+        <v>0</v>
       </c>
       <c r="E149">
-        <v>-10711800</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F149">
+        <v>2399.258037433171</v>
+      </c>
+      <c r="G149">
+        <v>1.44915652189912</v>
+      </c>
+      <c r="H149">
+        <v>39.37833006268175</v>
+      </c>
+      <c r="I149">
+        <v>2361.328863892388</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9">
       <c r="A150" s="2">
         <v>59171</v>
       </c>
@@ -2937,13 +4740,25 @@
         <v>0</v>
       </c>
       <c r="D150">
-        <v>10784835</v>
+        <v>0</v>
       </c>
       <c r="E150">
-        <v>-10784835</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F150">
+        <v>1760.157947567154</v>
+      </c>
+      <c r="G150">
+        <v>1.405893390717752</v>
+      </c>
+      <c r="H150">
+        <v>38.20024565499403</v>
+      </c>
+      <c r="I150">
+        <v>1723.363595302877</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9">
       <c r="A151" s="2">
         <v>59261</v>
       </c>
@@ -2954,13 +4769,25 @@
         <v>0</v>
       </c>
       <c r="D151">
-        <v>10857870</v>
+        <v>0</v>
       </c>
       <c r="E151">
-        <v>-10857870</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F151">
+        <v>1655.650406910639</v>
+      </c>
+      <c r="G151">
+        <v>0.914063825045033</v>
+      </c>
+      <c r="H151">
+        <v>37.35549226165399</v>
+      </c>
+      <c r="I151">
+        <v>1619.20897847403</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9">
       <c r="A152" s="2">
         <v>59352</v>
       </c>
@@ -2971,13 +4798,25 @@
         <v>0</v>
       </c>
       <c r="D152">
-        <v>10930905</v>
+        <v>0</v>
       </c>
       <c r="E152">
-        <v>-10930905</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F152">
+        <v>1598.68074444345</v>
+      </c>
+      <c r="G152">
+        <v>0</v>
+      </c>
+      <c r="H152">
+        <v>36.63305224190821</v>
+      </c>
+      <c r="I152">
+        <v>1562.047692201542</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9">
       <c r="A153" s="2">
         <v>59444</v>
       </c>
@@ -2988,13 +4827,25 @@
         <v>0</v>
       </c>
       <c r="D153">
-        <v>11003940</v>
+        <v>0</v>
       </c>
       <c r="E153">
-        <v>-11003940</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F153">
+        <v>1543.873839421048</v>
+      </c>
+      <c r="G153">
+        <v>0</v>
+      </c>
+      <c r="H153">
+        <v>35.84708120317446</v>
+      </c>
+      <c r="I153">
+        <v>1508.026758217873</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9">
       <c r="A154" s="2">
         <v>59536</v>
       </c>
@@ -3005,13 +4856,25 @@
         <v>0</v>
       </c>
       <c r="D154">
-        <v>11076975</v>
+        <v>0</v>
       </c>
       <c r="E154">
-        <v>-11076975</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F154">
+        <v>1491.078283428923</v>
+      </c>
+      <c r="G154">
+        <v>0</v>
+      </c>
+      <c r="H154">
+        <v>35.08147911895038</v>
+      </c>
+      <c r="I154">
+        <v>1455.996804309973</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9">
       <c r="A155" s="2">
         <v>59626</v>
       </c>
@@ -3022,13 +4885,25 @@
         <v>0</v>
       </c>
       <c r="D155">
-        <v>11150010</v>
+        <v>0</v>
       </c>
       <c r="E155">
-        <v>-11150010</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F155">
+        <v>1439.983429523533</v>
+      </c>
+      <c r="G155">
+        <v>0</v>
+      </c>
+      <c r="H155">
+        <v>34.33568733310408</v>
+      </c>
+      <c r="I155">
+        <v>1405.647742190429</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9">
       <c r="A156" s="2">
         <v>59717</v>
       </c>
@@ -3039,13 +4914,25 @@
         <v>0</v>
       </c>
       <c r="D156">
-        <v>11223045</v>
+        <v>0</v>
       </c>
       <c r="E156">
-        <v>-11223045</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F156">
+        <v>1397.608904937638</v>
+      </c>
+      <c r="G156">
+        <v>0</v>
+      </c>
+      <c r="H156">
+        <v>33.60948082185242</v>
+      </c>
+      <c r="I156">
+        <v>1363.999424115786</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9">
       <c r="A157" s="2">
         <v>59809</v>
       </c>
@@ -3056,13 +4943,25 @@
         <v>0</v>
       </c>
       <c r="D157">
-        <v>11296080</v>
+        <v>0</v>
       </c>
       <c r="E157">
-        <v>-11296080</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F157">
+        <v>1349.522993423419</v>
+      </c>
+      <c r="G157">
+        <v>0</v>
+      </c>
+      <c r="H157">
+        <v>32.90250006154805</v>
+      </c>
+      <c r="I157">
+        <v>1316.620493361871</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9">
       <c r="A158" s="2">
         <v>59901</v>
       </c>
@@ -3073,13 +4972,25 @@
         <v>0</v>
       </c>
       <c r="D158">
-        <v>11369115</v>
+        <v>0</v>
       </c>
       <c r="E158">
-        <v>-11369115</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F158">
+        <v>1303.226783136284</v>
+      </c>
+      <c r="G158">
+        <v>0</v>
+      </c>
+      <c r="H158">
+        <v>32.21418155325597</v>
+      </c>
+      <c r="I158">
+        <v>1271.012601583028</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9">
       <c r="A159" s="2">
         <v>59992</v>
       </c>
@@ -3090,13 +5001,25 @@
         <v>0</v>
       </c>
       <c r="D159">
-        <v>11442150</v>
+        <v>0</v>
       </c>
       <c r="E159">
-        <v>-11442150</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F159">
+        <v>1255.786911335008</v>
+      </c>
+      <c r="G159">
+        <v>0</v>
+      </c>
+      <c r="H159">
+        <v>31.54411867819512</v>
+      </c>
+      <c r="I159">
+        <v>1224.242792656813</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9">
       <c r="A160" s="2">
         <v>60083</v>
       </c>
@@ -3107,13 +5030,25 @@
         <v>0</v>
       </c>
       <c r="D160">
-        <v>11515185</v>
+        <v>0</v>
       </c>
       <c r="E160">
-        <v>-11515185</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F160">
+        <v>1204.716631944767</v>
+      </c>
+      <c r="G160">
+        <v>0</v>
+      </c>
+      <c r="H160">
+        <v>30.89396298964781</v>
+      </c>
+      <c r="I160">
+        <v>1173.82266895512</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9">
       <c r="A161" s="2">
         <v>60175</v>
       </c>
@@ -3124,13 +5059,25 @@
         <v>0</v>
       </c>
       <c r="D161">
-        <v>11588220</v>
+        <v>0</v>
       </c>
       <c r="E161">
-        <v>-11588220</v>
-      </c>
-    </row>
-    <row r="162" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F161">
+        <v>1155.863042680186</v>
+      </c>
+      <c r="G161">
+        <v>0</v>
+      </c>
+      <c r="H161">
+        <v>30.26441661441839</v>
+      </c>
+      <c r="I161">
+        <v>1125.598626065768</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9">
       <c r="A162" s="2">
         <v>60267</v>
       </c>
@@ -3141,13 +5088,25 @@
         <v>0</v>
       </c>
       <c r="D162">
-        <v>11661255</v>
+        <v>0</v>
       </c>
       <c r="E162">
-        <v>-11661255</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F162">
+        <v>1108.930811704767</v>
+      </c>
+      <c r="G162">
+        <v>0</v>
+      </c>
+      <c r="H162">
+        <v>29.65484110603622</v>
+      </c>
+      <c r="I162">
+        <v>1079.275970598731</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9">
       <c r="A163" s="2">
         <v>60357</v>
       </c>
@@ -3158,13 +5117,25 @@
         <v>0</v>
       </c>
       <c r="D163">
-        <v>11734290</v>
+        <v>0</v>
       </c>
       <c r="E163">
-        <v>-11734290</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F163">
+        <v>1281.873931950698</v>
+      </c>
+      <c r="G163">
+        <v>0</v>
+      </c>
+      <c r="H163">
+        <v>29.05425718553521</v>
+      </c>
+      <c r="I163">
+        <v>1252.819674765163</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9">
       <c r="A164" s="2">
         <v>60448</v>
       </c>
@@ -3175,13 +5146,25 @@
         <v>0</v>
       </c>
       <c r="D164">
-        <v>11807325</v>
+        <v>0</v>
       </c>
       <c r="E164">
-        <v>-11807325</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F164">
+        <v>1529.655526912219</v>
+      </c>
+      <c r="G164">
+        <v>0</v>
+      </c>
+      <c r="H164">
+        <v>28.3255024158502</v>
+      </c>
+      <c r="I164">
+        <v>1501.330024496369</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9">
       <c r="A165" s="2">
         <v>60540</v>
       </c>
@@ -3192,13 +5175,25 @@
         <v>0</v>
       </c>
       <c r="D165">
-        <v>11880360</v>
+        <v>0</v>
       </c>
       <c r="E165">
-        <v>-11880360</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F165">
+        <v>1184.609974519414</v>
+      </c>
+      <c r="G165">
+        <v>0</v>
+      </c>
+      <c r="H165">
+        <v>27.59032354899491</v>
+      </c>
+      <c r="I165">
+        <v>1157.019650970419</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9">
       <c r="A166" s="2">
         <v>60632</v>
       </c>
@@ -3209,13 +5204,25 @@
         <v>0</v>
       </c>
       <c r="D166">
-        <v>11953395</v>
+        <v>0</v>
       </c>
       <c r="E166">
-        <v>-11953395</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F166">
+        <v>972.0389650682354</v>
+      </c>
+      <c r="G166">
+        <v>0</v>
+      </c>
+      <c r="H166">
+        <v>26.99705805465306</v>
+      </c>
+      <c r="I166">
+        <v>945.0419070135823</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9">
       <c r="A167" s="2">
         <v>60722</v>
       </c>
@@ -3226,13 +5233,25 @@
         <v>0</v>
       </c>
       <c r="D167">
-        <v>12026430</v>
+        <v>0</v>
       </c>
       <c r="E167">
-        <v>-12026430</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F167">
+        <v>925.1551273391894</v>
+      </c>
+      <c r="G167">
+        <v>0</v>
+      </c>
+      <c r="H167">
+        <v>26.46341790875401</v>
+      </c>
+      <c r="I167">
+        <v>898.6917094304355</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9">
       <c r="A168" s="2">
         <v>60813</v>
       </c>
@@ -3243,13 +5262,25 @@
         <v>0</v>
       </c>
       <c r="D168">
-        <v>12099465</v>
+        <v>0</v>
       </c>
       <c r="E168">
-        <v>-12099465</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F168">
+        <v>893.5907983174385</v>
+      </c>
+      <c r="G168">
+        <v>0</v>
+      </c>
+      <c r="H168">
+        <v>25.94680192127549</v>
+      </c>
+      <c r="I168">
+        <v>867.6439963961629</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9">
       <c r="A169" s="2">
         <v>60905</v>
       </c>
@@ -3260,13 +5291,25 @@
         <v>0</v>
       </c>
       <c r="D169">
-        <v>12172500</v>
+        <v>0</v>
       </c>
       <c r="E169">
-        <v>-12172500</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F169">
+        <v>863.2608991525897</v>
+      </c>
+      <c r="G169">
+        <v>0</v>
+      </c>
+      <c r="H169">
+        <v>25.44423492030354</v>
+      </c>
+      <c r="I169">
+        <v>837.816664232286</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9">
       <c r="A170" s="2">
         <v>60997</v>
       </c>
@@ -3277,13 +5320,25 @@
         <v>0</v>
       </c>
       <c r="D170">
-        <v>12245535</v>
+        <v>0</v>
       </c>
       <c r="E170">
-        <v>-12245535</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F170">
+        <v>834.0673594367231</v>
+      </c>
+      <c r="G170">
+        <v>0</v>
+      </c>
+      <c r="H170">
+        <v>24.95528593526339</v>
+      </c>
+      <c r="I170">
+        <v>809.1120735014597</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9">
       <c r="A171" s="2">
         <v>61087</v>
       </c>
@@ -3294,13 +5349,25 @@
         <v>0</v>
       </c>
       <c r="D171">
-        <v>12318570</v>
+        <v>0</v>
       </c>
       <c r="E171">
-        <v>-12318570</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F171">
+        <v>805.8826126230067</v>
+      </c>
+      <c r="G171">
+        <v>0</v>
+      </c>
+      <c r="H171">
+        <v>24.47955428258319</v>
+      </c>
+      <c r="I171">
+        <v>781.4030583404235</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9">
       <c r="A172" s="2">
         <v>61178</v>
       </c>
@@ -3311,13 +5378,25 @@
         <v>0</v>
       </c>
       <c r="D172">
-        <v>12391605</v>
+        <v>0</v>
       </c>
       <c r="E172">
-        <v>-12391605</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F172">
+        <v>778.5930577964521</v>
+      </c>
+      <c r="G172">
+        <v>0</v>
+      </c>
+      <c r="H172">
+        <v>24.01678412911856</v>
+      </c>
+      <c r="I172">
+        <v>754.5762736673335</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9">
       <c r="A173" s="2">
         <v>61270</v>
       </c>
@@ -3328,13 +5407,25 @@
         <v>0</v>
       </c>
       <c r="D173">
-        <v>12464640</v>
+        <v>0</v>
       </c>
       <c r="E173">
-        <v>-12464640</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F173">
+        <v>752.3290475637559</v>
+      </c>
+      <c r="G173">
+        <v>0</v>
+      </c>
+      <c r="H173">
+        <v>23.56667100395116</v>
+      </c>
+      <c r="I173">
+        <v>728.7623765598047</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9">
       <c r="A174" s="2">
         <v>61362</v>
       </c>
@@ -3345,13 +5436,25 @@
         <v>0</v>
       </c>
       <c r="D174">
-        <v>12537675</v>
+        <v>0</v>
       </c>
       <c r="E174">
-        <v>-12537675</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F174">
+        <v>727.0489958772113</v>
+      </c>
+      <c r="G174">
+        <v>0</v>
+      </c>
+      <c r="H174">
+        <v>23.1288320990973</v>
+      </c>
+      <c r="I174">
+        <v>703.920163778114</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9">
       <c r="A175" s="2">
         <v>61453</v>
       </c>
@@ -3362,13 +5465,25 @@
         <v>0</v>
       </c>
       <c r="D175">
-        <v>12610710</v>
+        <v>0</v>
       </c>
       <c r="E175">
-        <v>-12610710</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F175">
+        <v>702.6444816842896</v>
+      </c>
+      <c r="G175">
+        <v>0</v>
+      </c>
+      <c r="H175">
+        <v>22.70290529213354</v>
+      </c>
+      <c r="I175">
+        <v>679.9415763921561</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9">
       <c r="A176" s="2">
         <v>61544</v>
       </c>
@@ -3379,13 +5494,25 @@
         <v>0</v>
       </c>
       <c r="D176">
-        <v>12683745</v>
+        <v>0</v>
       </c>
       <c r="E176">
-        <v>-12683745</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F176">
+        <v>679.0186668329877</v>
+      </c>
+      <c r="G176">
+        <v>0</v>
+      </c>
+      <c r="H176">
+        <v>22.28865512738771</v>
+      </c>
+      <c r="I176">
+        <v>656.7300117056</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9">
       <c r="A177" s="2">
         <v>61636</v>
       </c>
@@ -3396,13 +5523,25 @@
         <v>0</v>
       </c>
       <c r="D177">
-        <v>12756780</v>
+        <v>0</v>
       </c>
       <c r="E177">
-        <v>-12756780</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F177">
+        <v>656.2794031023352</v>
+      </c>
+      <c r="G177">
+        <v>0</v>
+      </c>
+      <c r="H177">
+        <v>21.88580467234322</v>
+      </c>
+      <c r="I177">
+        <v>634.3935984299919</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9">
       <c r="A178" s="2">
         <v>61728</v>
       </c>
@@ -3413,13 +5552,25 @@
         <v>0</v>
       </c>
       <c r="D178">
-        <v>12829815</v>
+        <v>0</v>
       </c>
       <c r="E178">
-        <v>-12829815</v>
-      </c>
-    </row>
-    <row r="179" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F178">
+        <v>634.3906148287123</v>
+      </c>
+      <c r="G178">
+        <v>0</v>
+      </c>
+      <c r="H178">
+        <v>21.49400948887508</v>
+      </c>
+      <c r="I178">
+        <v>612.8966053398372</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9">
       <c r="A179" s="2">
         <v>61818</v>
       </c>
@@ -3430,13 +5581,25 @@
         <v>0</v>
       </c>
       <c r="D179">
-        <v>12902850</v>
+        <v>0</v>
       </c>
       <c r="E179">
-        <v>-12902850</v>
-      </c>
-    </row>
-    <row r="180" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F179">
+        <v>608.0237222877493</v>
+      </c>
+      <c r="G179">
+        <v>0</v>
+      </c>
+      <c r="H179">
+        <v>21.11352086158202</v>
+      </c>
+      <c r="I179">
+        <v>586.9102014261672</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9">
       <c r="A180" s="2">
         <v>61909</v>
       </c>
@@ -3447,13 +5610,25 @@
         <v>0</v>
       </c>
       <c r="D180">
-        <v>12975885</v>
+        <v>0</v>
       </c>
       <c r="E180">
-        <v>-12975885</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F180">
+        <v>572.5110477379187</v>
+      </c>
+      <c r="G180">
+        <v>0</v>
+      </c>
+      <c r="H180">
+        <v>20.75322198016699</v>
+      </c>
+      <c r="I180">
+        <v>551.7578257577518</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9">
       <c r="A181" s="2">
         <v>62001</v>
       </c>
@@ -3464,13 +5639,25 @@
         <v>0</v>
       </c>
       <c r="D181">
-        <v>13048920</v>
+        <v>0</v>
       </c>
       <c r="E181">
-        <v>-13048920</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F181">
+        <v>538.683434602906</v>
+      </c>
+      <c r="G181">
+        <v>0</v>
+      </c>
+      <c r="H181">
+        <v>20.41814028091934</v>
+      </c>
+      <c r="I181">
+        <v>518.2652943219866</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9">
       <c r="A182" s="2">
         <v>62093</v>
       </c>
@@ -3481,13 +5668,25 @@
         <v>0</v>
       </c>
       <c r="D182">
-        <v>13121955</v>
+        <v>0</v>
       </c>
       <c r="E182">
-        <v>-13121955</v>
-      </c>
-    </row>
-    <row r="183" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F182">
+        <v>506.1553607187036</v>
+      </c>
+      <c r="G182">
+        <v>0</v>
+      </c>
+      <c r="H182">
+        <v>20.10763795983933</v>
+      </c>
+      <c r="I182">
+        <v>486.0477227588643</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9">
       <c r="A183" s="2">
         <v>62183</v>
       </c>
@@ -3498,13 +5697,25 @@
         <v>0</v>
       </c>
       <c r="D183">
-        <v>13194990</v>
+        <v>0</v>
       </c>
       <c r="E183">
-        <v>-13194990</v>
-      </c>
-    </row>
-    <row r="184" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F183">
+        <v>1008.176079693148</v>
+      </c>
+      <c r="G183">
+        <v>0</v>
+      </c>
+      <c r="H183">
+        <v>19.75919825865885</v>
+      </c>
+      <c r="I183">
+        <v>988.4168814344895</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9">
       <c r="A184" s="2">
         <v>62274</v>
       </c>
@@ -3515,13 +5726,25 @@
         <v>0</v>
       </c>
       <c r="D184">
-        <v>13268025</v>
+        <v>0</v>
       </c>
       <c r="E184">
-        <v>-13268025</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F184">
+        <v>1689.554092476013</v>
+      </c>
+      <c r="G184">
+        <v>0</v>
+      </c>
+      <c r="H184">
+        <v>18.55776976911735</v>
+      </c>
+      <c r="I184">
+        <v>1670.996322706896</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9">
       <c r="A185" s="2">
         <v>62366</v>
       </c>
@@ -3532,13 +5755,25 @@
         <v>0</v>
       </c>
       <c r="D185">
-        <v>13341060</v>
+        <v>0</v>
       </c>
       <c r="E185">
-        <v>-13341060</v>
-      </c>
-    </row>
-    <row r="186" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F185">
+        <v>915.490019657105</v>
+      </c>
+      <c r="G185">
+        <v>0</v>
+      </c>
+      <c r="H185">
+        <v>17.23136575416074</v>
+      </c>
+      <c r="I185">
+        <v>898.2586539029443</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9">
       <c r="A186" s="2">
         <v>62458</v>
       </c>
@@ -3549,13 +5784,25 @@
         <v>0</v>
       </c>
       <c r="D186">
-        <v>13414095</v>
+        <v>0</v>
       </c>
       <c r="E186">
-        <v>-13414095</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F186">
+        <v>462.6530330128983</v>
+      </c>
+      <c r="G186">
+        <v>0</v>
+      </c>
+      <c r="H186">
+        <v>16.66919193111774</v>
+      </c>
+      <c r="I186">
+        <v>445.9838410817806</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9">
       <c r="A187" s="2">
         <v>62548</v>
       </c>
@@ -3566,13 +5813,25 @@
         <v>0</v>
       </c>
       <c r="D187">
-        <v>13487130</v>
+        <v>0</v>
       </c>
       <c r="E187">
-        <v>-13487130</v>
-      </c>
-    </row>
-    <row r="188" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F187">
+        <v>400.6063423822642</v>
+      </c>
+      <c r="G187">
+        <v>0</v>
+      </c>
+      <c r="H187">
+        <v>16.38495518965176</v>
+      </c>
+      <c r="I187">
+        <v>384.2213871926124</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9">
       <c r="A188" s="2">
         <v>62639</v>
       </c>
@@ -3583,13 +5842,25 @@
         <v>0</v>
       </c>
       <c r="D188">
-        <v>13560165</v>
+        <v>0</v>
       </c>
       <c r="E188">
-        <v>-13560165</v>
-      </c>
-    </row>
-    <row r="189" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F188">
+        <v>349.7719571163873</v>
+      </c>
+      <c r="G188">
+        <v>0</v>
+      </c>
+      <c r="H188">
+        <v>16.14995612025244</v>
+      </c>
+      <c r="I188">
+        <v>333.6220009961348</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9">
       <c r="A189" s="2">
         <v>62731</v>
       </c>
@@ -3600,13 +5871,25 @@
         <v>0</v>
       </c>
       <c r="D189">
-        <v>13633200</v>
+        <v>0</v>
       </c>
       <c r="E189">
-        <v>-13633200</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F189">
+        <v>301.7221527270303</v>
+      </c>
+      <c r="G189">
+        <v>0</v>
+      </c>
+      <c r="H189">
+        <v>15.9623835037707</v>
+      </c>
+      <c r="I189">
+        <v>285.7597692232596</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9">
       <c r="A190" s="2">
         <v>62823</v>
       </c>
@@ -3617,13 +5900,25 @@
         <v>0</v>
       </c>
       <c r="D190">
-        <v>13706235</v>
+        <v>0</v>
       </c>
       <c r="E190">
-        <v>-13706235</v>
-      </c>
-    </row>
-    <row r="191" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F190">
+        <v>255.5096562053758</v>
+      </c>
+      <c r="G190">
+        <v>0</v>
+      </c>
+      <c r="H190">
+        <v>15.82119298016681</v>
+      </c>
+      <c r="I190">
+        <v>239.688463225209</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9">
       <c r="A191" s="2">
         <v>62914</v>
       </c>
@@ -3634,13 +5929,25 @@
         <v>0</v>
       </c>
       <c r="D191">
-        <v>13779270</v>
+        <v>0</v>
       </c>
       <c r="E191">
-        <v>-13779270</v>
-      </c>
-    </row>
-    <row r="192" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F191">
+        <v>1627.737561088898</v>
+      </c>
+      <c r="G191">
+        <v>0</v>
+      </c>
+      <c r="H191">
+        <v>15.54755095853439</v>
+      </c>
+      <c r="I191">
+        <v>1612.190010130363</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9">
       <c r="A192" s="2">
         <v>63005</v>
       </c>
@@ -3651,13 +5958,25 @@
         <v>0</v>
       </c>
       <c r="D192">
-        <v>13852305</v>
+        <v>0</v>
       </c>
       <c r="E192">
-        <v>-13852305</v>
-      </c>
-    </row>
-    <row r="193" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F192">
+        <v>3449.517285679144</v>
+      </c>
+      <c r="G192">
+        <v>0</v>
+      </c>
+      <c r="H192">
+        <v>12.80851502220217</v>
+      </c>
+      <c r="I192">
+        <v>3436.708770656942</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9">
       <c r="A193" s="2">
         <v>63097</v>
       </c>
@@ -3668,13 +5987,25 @@
         <v>0</v>
       </c>
       <c r="D193">
-        <v>13925340</v>
+        <v>0</v>
       </c>
       <c r="E193">
-        <v>-13925340</v>
-      </c>
-    </row>
-    <row r="194" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F193">
+        <v>1366.857917730821</v>
+      </c>
+      <c r="G193">
+        <v>0</v>
+      </c>
+      <c r="H193">
+        <v>9.740433878382044</v>
+      </c>
+      <c r="I193">
+        <v>1357.117483852439</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9">
       <c r="A194" s="2">
         <v>63189</v>
       </c>
@@ -3685,13 +6016,25 @@
         <v>0</v>
       </c>
       <c r="D194">
-        <v>13998375</v>
+        <v>0</v>
       </c>
       <c r="E194">
-        <v>-13998375</v>
-      </c>
-    </row>
-    <row r="195" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F194">
+        <v>148.2840515504658</v>
+      </c>
+      <c r="G194">
+        <v>0</v>
+      </c>
+      <c r="H194">
+        <v>8.923258758536138</v>
+      </c>
+      <c r="I194">
+        <v>139.3607927919297</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9">
       <c r="A195" s="2">
         <v>63279</v>
       </c>
@@ -3702,13 +6045,25 @@
         <v>0</v>
       </c>
       <c r="D195">
-        <v>14071410</v>
+        <v>0</v>
       </c>
       <c r="E195">
-        <v>-14071410</v>
-      </c>
-    </row>
-    <row r="196" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F195">
+        <v>1618.866264685718</v>
+      </c>
+      <c r="G195">
+        <v>0</v>
+      </c>
+      <c r="H195">
+        <v>8.699700301577405</v>
+      </c>
+      <c r="I195">
+        <v>1610.16656438414</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9">
       <c r="A196" s="2">
         <v>63370</v>
       </c>
@@ -3719,13 +6074,25 @@
         <v>0</v>
       </c>
       <c r="D196">
-        <v>14144445</v>
+        <v>0</v>
       </c>
       <c r="E196">
-        <v>-14144445</v>
-      </c>
-    </row>
-    <row r="197" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F196">
+        <v>3716.206777555433</v>
+      </c>
+      <c r="G196">
+        <v>0</v>
+      </c>
+      <c r="H196">
+        <v>5.188593205325525</v>
+      </c>
+      <c r="I196">
+        <v>3711.018184350108</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9">
       <c r="A197" s="2">
         <v>63462</v>
       </c>
@@ -3736,13 +6103,25 @@
         <v>0</v>
       </c>
       <c r="D197">
-        <v>14217480</v>
+        <v>0</v>
       </c>
       <c r="E197">
-        <v>-14217480</v>
-      </c>
-    </row>
-    <row r="198" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F197">
+        <v>1427.095578639947</v>
+      </c>
+      <c r="G197">
+        <v>0</v>
+      </c>
+      <c r="H197">
+        <v>1.162688432308905</v>
+      </c>
+      <c r="I197">
+        <v>1425.932890207638</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9">
       <c r="A198" s="2">
         <v>63554</v>
       </c>
@@ -3753,13 +6132,25 @@
         <v>0</v>
       </c>
       <c r="D198">
-        <v>14290515</v>
+        <v>0</v>
       </c>
       <c r="E198">
-        <v>-14290515</v>
-      </c>
-    </row>
-    <row r="199" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F198">
+        <v>106.3654294424856</v>
+      </c>
+      <c r="G198">
+        <v>0</v>
+      </c>
+      <c r="H198">
+        <v>0.06176544452784628</v>
+      </c>
+      <c r="I198">
+        <v>106.3036639979577</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9">
       <c r="A199" s="2">
         <v>63644</v>
       </c>
@@ -3770,13 +6161,25 @@
         <v>0</v>
       </c>
       <c r="D199">
-        <v>14363550</v>
+        <v>0</v>
       </c>
       <c r="E199">
-        <v>-14363550</v>
-      </c>
-    </row>
-    <row r="200" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F199">
+        <v>0.3714462795829466</v>
+      </c>
+      <c r="G199">
+        <v>0</v>
+      </c>
+      <c r="H199">
+        <v>0.0001679993188169991</v>
+      </c>
+      <c r="I199">
+        <v>0.3712782802641296</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9">
       <c r="A200" s="2">
         <v>63735</v>
       </c>
@@ -3787,13 +6190,25 @@
         <v>0</v>
       </c>
       <c r="D200">
-        <v>14436585</v>
+        <v>0</v>
       </c>
       <c r="E200">
-        <v>-14436585</v>
-      </c>
-    </row>
-    <row r="201" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F200">
+        <v>0</v>
+      </c>
+      <c r="G200">
+        <v>0</v>
+      </c>
+      <c r="H200">
+        <v>0</v>
+      </c>
+      <c r="I200">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9">
       <c r="A201" s="2">
         <v>63827</v>
       </c>
@@ -3804,13 +6219,25 @@
         <v>0</v>
       </c>
       <c r="D201">
-        <v>14509620</v>
+        <v>0</v>
       </c>
       <c r="E201">
-        <v>-14509620</v>
-      </c>
-    </row>
-    <row r="202" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="F201">
+        <v>0</v>
+      </c>
+      <c r="G201">
+        <v>0</v>
+      </c>
+      <c r="H201">
+        <v>0</v>
+      </c>
+      <c r="I201">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9">
       <c r="A202" s="2">
         <v>63919</v>
       </c>
@@ -3821,10 +6248,22 @@
         <v>0</v>
       </c>
       <c r="D202">
-        <v>14582655</v>
+        <v>0</v>
       </c>
       <c r="E202">
-        <v>-14582655</v>
+        <v>0</v>
+      </c>
+      <c r="F202">
+        <v>0</v>
+      </c>
+      <c r="G202">
+        <v>0</v>
+      </c>
+      <c r="H202">
+        <v>0</v>
+      </c>
+      <c r="I202">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3834,1619 +6273,2225 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B202"/>
+  <dimension ref="A1:C202"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>8</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="2">
         <v>45657</v>
       </c>
       <c r="B2">
-        <v>597468254.5500045</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>2002433.22</v>
+      </c>
+      <c r="C2">
+        <v>2002433.22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" s="2">
         <v>45747</v>
       </c>
       <c r="B3">
-        <v>594459709.2185394</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>2030894.276755791</v>
+      </c>
+      <c r="C3">
+        <v>2030894.276755791</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" s="2">
         <v>45838</v>
       </c>
       <c r="B4">
-        <v>591466313.3863076</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>2059779.631019012</v>
+      </c>
+      <c r="C4">
+        <v>2059779.631019012</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="2">
         <v>45930</v>
       </c>
       <c r="B5">
-        <v>588487990.7685752</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>2089095.890825701</v>
+      </c>
+      <c r="C5">
+        <v>2089095.890825701</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="2">
         <v>46022</v>
       </c>
       <c r="B6">
-        <v>585524665.4642222</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>2118849.771010265</v>
+      </c>
+      <c r="C6">
+        <v>2118849.771010265</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" s="2">
         <v>46112</v>
       </c>
       <c r="B7">
-        <v>581275553.8493518</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>2090414.957729264</v>
+      </c>
+      <c r="C7">
+        <v>2131115.064094459</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" s="2">
         <v>46203</v>
       </c>
       <c r="B8">
-        <v>577057277.7410939</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>2061682.58520477</v>
+      </c>
+      <c r="C8">
+        <v>2107119.697518569</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9" s="2">
         <v>46295</v>
       </c>
       <c r="B9">
-        <v>572869613.3677915</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>2032825.127039074</v>
+      </c>
+      <c r="C9">
+        <v>2079167.807979091</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
       <c r="A10" s="2">
         <v>46387</v>
       </c>
       <c r="B10">
-        <v>568712338.5823612</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>2003988.996509367</v>
+      </c>
+      <c r="C10">
+        <v>2061437.967612841</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11" s="2">
         <v>46477</v>
       </c>
       <c r="B11">
-        <v>563143184.6230956</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
+        <v>1967891.928793207</v>
+      </c>
+      <c r="C11">
+        <v>2044116.028633488</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12" s="2">
         <v>46568</v>
       </c>
       <c r="B12">
-        <v>557628566.9797266</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+        <v>1932208.516517321</v>
+      </c>
+      <c r="C12">
+        <v>2025796.364310259</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13" s="2">
         <v>46660</v>
       </c>
       <c r="B13">
-        <v>552167951.6017482</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
+        <v>1897059.812520349</v>
+      </c>
+      <c r="C13">
+        <v>2006564.641574032</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14" s="2">
         <v>46752</v>
       </c>
       <c r="B14">
-        <v>546760809.6685551</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
+        <v>1862542.447494138</v>
+      </c>
+      <c r="C14">
+        <v>1986510.288407409</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15" s="2">
         <v>46843</v>
       </c>
       <c r="B15">
-        <v>539851786.2057233</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
+        <v>1820923.994030168</v>
+      </c>
+      <c r="C15">
+        <v>1965721.074887053</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16" s="2">
         <v>46934</v>
       </c>
       <c r="B16">
-        <v>533030067.1076097</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
+        <v>1780395.558876032</v>
+      </c>
+      <c r="C16">
+        <v>1944269.080784836</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17" s="2">
         <v>47026</v>
       </c>
       <c r="B17">
-        <v>526294549.1720224</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
+        <v>1741014.004875531</v>
+      </c>
+      <c r="C17">
+        <v>1922212.389792986</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" s="2">
         <v>47118</v>
       </c>
       <c r="B18">
-        <v>519644143.1363826</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
+        <v>1702816.19997311</v>
+      </c>
+      <c r="C18">
+        <v>1899611.28675142</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" s="2">
         <v>47208</v>
       </c>
       <c r="B19">
-        <v>511420263.3896087</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
+        <v>1657934.487392292</v>
+      </c>
+      <c r="C19">
+        <v>1876252.476870257</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20" s="2">
         <v>47299</v>
       </c>
       <c r="B20">
-        <v>503326534.6298706</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
+        <v>1614718.722799017</v>
+      </c>
+      <c r="C20">
+        <v>1852481.463133894</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21" s="2">
         <v>47391</v>
       </c>
       <c r="B21">
-        <v>495360897.0894532</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
+        <v>1573157.715084777</v>
+      </c>
+      <c r="C21">
+        <v>1828361.106445521</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22" s="2">
         <v>47483</v>
       </c>
       <c r="B22">
-        <v>487521323.5992366</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
+        <v>1533226.966701879</v>
+      </c>
+      <c r="C22">
+        <v>1803949.153809539</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23" s="2">
         <v>47573</v>
       </c>
       <c r="B23">
-        <v>478071091.0505118</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
+        <v>1487361.995978832</v>
+      </c>
+      <c r="C23">
+        <v>1778836.869152639</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
       <c r="A24" s="2">
         <v>47664</v>
       </c>
       <c r="B24">
-        <v>468804044.1201892</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
+        <v>1443593.135537254</v>
+      </c>
+      <c r="C24">
+        <v>1753532.831790598</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
       <c r="A25" s="2">
         <v>47756</v>
       </c>
       <c r="B25">
-        <v>459716631.8938127</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
+        <v>1401844.596365808</v>
+      </c>
+      <c r="C25">
+        <v>1728078.322163336</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
       <c r="A26" s="2">
         <v>47848</v>
       </c>
       <c r="B26">
-        <v>450805372.2879463</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
+        <v>1362035.709024001</v>
+      </c>
+      <c r="C26">
+        <v>1702511.032481097</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
       <c r="A27" s="2">
         <v>47938</v>
       </c>
       <c r="B27">
-        <v>440301580.6134771</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
+        <v>1290540.861248743</v>
+      </c>
+      <c r="C27">
+        <v>1676215.696701225</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
       <c r="A28" s="2">
         <v>48029</v>
       </c>
       <c r="B28">
-        <v>430042527.9024788</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
+        <v>1250567.194194839</v>
+      </c>
+      <c r="C28">
+        <v>1649940.61526454</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
       <c r="A29" s="2">
         <v>48121</v>
       </c>
       <c r="B29">
-        <v>420022511.7228613</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
+        <v>1212651.014406957</v>
+      </c>
+      <c r="C29">
+        <v>1623715.922548464</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
       <c r="A30" s="2">
         <v>48213</v>
       </c>
       <c r="B30">
-        <v>410235962.5090909</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
+        <v>1176662.004959901</v>
+      </c>
+      <c r="C30">
+        <v>1597568.927907542</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
       <c r="A31" s="2">
         <v>48304</v>
       </c>
       <c r="B31">
-        <v>398912432.7525842</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
+        <v>1119154.923386913</v>
+      </c>
+      <c r="C31">
+        <v>1571466.423422763</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
       <c r="A32" s="2">
         <v>48395</v>
       </c>
       <c r="B32">
-        <v>387901460.4943697</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
+        <v>1083684.266754133</v>
+      </c>
+      <c r="C32">
+        <v>1545436.664841921</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
       <c r="A33" s="2">
         <v>48487</v>
       </c>
       <c r="B33">
-        <v>377194418.3723776</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
+        <v>1049974.251065153</v>
+      </c>
+      <c r="C33">
+        <v>1519508.636744153</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34" s="2">
         <v>48579</v>
       </c>
       <c r="B34">
-        <v>366782917.1614652</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
+        <v>1017930.557214363</v>
+      </c>
+      <c r="C34">
+        <v>1493709.050023289</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35" s="2">
         <v>48669</v>
       </c>
       <c r="B35">
-        <v>354916657.9365832</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
+        <v>982404.309115221</v>
+      </c>
+      <c r="C35">
+        <v>1467890.141552921</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
       <c r="A36" s="2">
         <v>48760</v>
       </c>
       <c r="B36">
-        <v>343434299.1100468</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
+        <v>948827.9777534606</v>
+      </c>
+      <c r="C36">
+        <v>1442339.794061798</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37" s="2">
         <v>48852</v>
       </c>
       <c r="B37">
-        <v>332323420.6332442</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
+        <v>917085.739324851</v>
+      </c>
+      <c r="C37">
+        <v>1417063.124100314</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38" s="2">
         <v>48944</v>
       </c>
       <c r="B38">
-        <v>321572004.2742723</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
+        <v>887069.3017553007</v>
+      </c>
+      <c r="C38">
+        <v>1392064.816531939</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
       <c r="A39" s="2">
         <v>49034</v>
       </c>
       <c r="B39">
-        <v>309479380.3555083</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
+        <v>854200.8152815395</v>
+      </c>
+      <c r="C39">
+        <v>1367344.932770514</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
       <c r="A40" s="2">
         <v>49125</v>
       </c>
       <c r="B40">
-        <v>297841496.1257959</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
+        <v>823302.5961186949</v>
+      </c>
+      <c r="C40">
+        <v>1342897.784841097</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
       <c r="A41" s="2">
         <v>49217</v>
       </c>
       <c r="B41">
-        <v>286641251.2283305</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
+        <v>794245.8732633025</v>
+      </c>
+      <c r="C41">
+        <v>1318725.512285997</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
       <c r="A42" s="2">
         <v>49309</v>
       </c>
       <c r="B42">
-        <v>275862188.3601884</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
+        <v>766910.9207227102</v>
+      </c>
+      <c r="C42">
+        <v>1294830.680748911</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
       <c r="A43" s="2">
         <v>49399</v>
       </c>
       <c r="B43">
-        <v>263971507.0026341</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
+        <v>731316.0209859672</v>
+      </c>
+      <c r="C43">
+        <v>1271136.256561959</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
       <c r="A44" s="2">
         <v>49490</v>
       </c>
       <c r="B44">
-        <v>252593358.0220896</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
+        <v>704360.7026735203</v>
+      </c>
+      <c r="C44">
+        <v>1247700.383349814</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
       <c r="A45" s="2">
         <v>49582</v>
       </c>
       <c r="B45">
-        <v>241705649.3761598</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
+        <v>679082.2849328296</v>
+      </c>
+      <c r="C45">
+        <v>1224526.811317703</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
       <c r="A46" s="2">
         <v>49674</v>
       </c>
       <c r="B46">
-        <v>231287241.2711636</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
+        <v>655367.6364342798</v>
+      </c>
+      <c r="C46">
+        <v>1201619.566494463</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
       <c r="A47" s="2">
         <v>49765</v>
       </c>
       <c r="B47">
-        <v>219922852.3438639</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
+        <v>629699.5808697146</v>
+      </c>
+      <c r="C47">
+        <v>1178985.744831461</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
       <c r="A48" s="2">
         <v>49856</v>
       </c>
       <c r="B48">
-        <v>209116857.1048422</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
+        <v>605759.7954794454</v>
+      </c>
+      <c r="C48">
+        <v>1156634.655073488</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
       <c r="A49" s="2">
         <v>49948</v>
       </c>
       <c r="B49">
-        <v>198841818.6620199</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
+        <v>583418.0532609639</v>
+      </c>
+      <c r="C49">
+        <v>1134569.341131968</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
       <c r="A50" s="2">
         <v>50040</v>
       </c>
       <c r="B50">
-        <v>189071648.2459737</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
+        <v>562554.1210091125</v>
+      </c>
+      <c r="C50">
+        <v>1112792.905760715</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
       <c r="A51" s="2">
         <v>50130</v>
       </c>
       <c r="B51">
-        <v>178533342.5845001</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
+        <v>540050.3655701827</v>
+      </c>
+      <c r="C51">
+        <v>1091309.682618476</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
       <c r="A52" s="2">
         <v>50221</v>
       </c>
       <c r="B52">
-        <v>168582411.5360227</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
+        <v>519148.2209257639</v>
+      </c>
+      <c r="C52">
+        <v>1070124.083733816</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
       <c r="A53" s="2">
         <v>50313</v>
       </c>
       <c r="B53">
-        <v>159186116.5420905</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
+        <v>499714.1319333865</v>
+      </c>
+      <c r="C53">
+        <v>1049237.209322492</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
       <c r="A54" s="2">
         <v>50405</v>
       </c>
       <c r="B54">
-        <v>150313543.7965342</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
+        <v>481626.0193901812</v>
+      </c>
+      <c r="C54">
+        <v>1028650.162611971</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
       <c r="A55" s="2">
         <v>50495</v>
       </c>
       <c r="B55">
-        <v>140849040.4003476</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
+        <v>462144.7256689764</v>
+      </c>
+      <c r="C55">
+        <v>1008376.701139648</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
       <c r="A56" s="2">
         <v>50586</v>
       </c>
       <c r="B56">
-        <v>131980470.1600875</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
+        <v>444094.6194433533</v>
+      </c>
+      <c r="C56">
+        <v>988439.9096393128</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
       <c r="A57" s="2">
         <v>50678</v>
       </c>
       <c r="B57">
-        <v>123670310.1005964</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
+        <v>427345.2025281118</v>
+      </c>
+      <c r="C57">
+        <v>968834.9595557892</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
       <c r="A58" s="2">
         <v>50770</v>
       </c>
       <c r="B58">
-        <v>115883399.8834872</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
+        <v>411778.4639237812</v>
+      </c>
+      <c r="C58">
+        <v>949557.1938439604</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
       <c r="A59" s="2">
         <v>50860</v>
       </c>
       <c r="B59">
-        <v>107674579.2754233</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
+        <v>394999.7387768329</v>
+      </c>
+      <c r="C59">
+        <v>930599.1859112852</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
       <c r="A60" s="2">
         <v>50951</v>
       </c>
       <c r="B60">
-        <v>100047246.0576275</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
+        <v>379456.6833419634</v>
+      </c>
+      <c r="C60">
+        <v>911951.4653893212</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
       <c r="A61" s="2">
         <v>51043</v>
       </c>
       <c r="B61">
-        <v>92960209.46699306</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
+        <v>365028.3266044731</v>
+      </c>
+      <c r="C61">
+        <v>893611.0675196425</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
       <c r="A62" s="2">
         <v>51135</v>
       </c>
       <c r="B62">
-        <v>86375196.56635068</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
+        <v>351606.4841651663</v>
+      </c>
+      <c r="C62">
+        <v>875575.0771536165</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
       <c r="A63" s="2">
         <v>51226</v>
       </c>
       <c r="B63">
-        <v>79521965.6888189</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
+        <v>327185.236243183</v>
+      </c>
+      <c r="C63">
+        <v>857771.263838722</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
       <c r="A64" s="2">
         <v>51317</v>
       </c>
       <c r="B64">
-        <v>73212487.82519579</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2">
+        <v>315004.4026354912</v>
+      </c>
+      <c r="C64">
+        <v>840232.9196233989</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
       <c r="A65" s="2">
         <v>51409</v>
       </c>
       <c r="B65">
-        <v>67403620.20893082</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2">
+        <v>303587.7291309127</v>
+      </c>
+      <c r="C65">
+        <v>822959.6870576229</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
       <c r="A66" s="2">
         <v>51501</v>
       </c>
       <c r="B66">
-        <v>62055643.13175521</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2">
+        <v>292863.1149193191</v>
+      </c>
+      <c r="C66">
+        <v>805951.0959131926</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
       <c r="A67" s="2">
         <v>51591</v>
       </c>
       <c r="B67">
-        <v>56562972.60468512</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2">
+        <v>270766.3039800997</v>
+      </c>
+      <c r="C67">
+        <v>789226.9992309676</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
       <c r="A68" s="2">
         <v>51682</v>
       </c>
       <c r="B68">
-        <v>51556469.45898152</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2">
+        <v>261086.2715262183</v>
+      </c>
+      <c r="C68">
+        <v>772823.93281691</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
       <c r="A69" s="2">
         <v>51774</v>
       </c>
       <c r="B69">
-        <v>46993102.03603938</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2">
+        <v>251888.0967924453</v>
+      </c>
+      <c r="C69">
+        <v>756734.707427353</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
       <c r="A70" s="2">
         <v>51866</v>
       </c>
       <c r="B70">
-        <v>42833647.49650557</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2">
+        <v>243133.4386401206</v>
+      </c>
+      <c r="C70">
+        <v>740952.3018160259</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
       <c r="A71" s="2">
         <v>51956</v>
       </c>
       <c r="B71">
-        <v>38615315.00793547</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2">
+        <v>222470.693877939</v>
+      </c>
+      <c r="C71">
+        <v>725346.5918402516</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
       <c r="A72" s="2">
         <v>52047</v>
       </c>
       <c r="B72">
-        <v>34812411.27747011</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2">
+        <v>214692.3580148165</v>
+      </c>
+      <c r="C72">
+        <v>710036.0707287794</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
       <c r="A73" s="2">
         <v>52139</v>
       </c>
       <c r="B73">
-        <v>31384024.15473477</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2">
+        <v>207167.9398656372</v>
+      </c>
+      <c r="C73">
+        <v>695012.2463075148</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
       <c r="A74" s="2">
         <v>52231</v>
       </c>
       <c r="B74">
-        <v>28293270.58945553</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2">
+        <v>199891.6137861555</v>
+      </c>
+      <c r="C74">
+        <v>680266.995353383</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
       <c r="A75" s="2">
         <v>52321</v>
       </c>
       <c r="B75">
-        <v>25198452.72407024</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2">
+        <v>191682.7288283924</v>
+      </c>
+      <c r="C75">
+        <v>665582.7386262607</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
       <c r="A76" s="2">
         <v>52412</v>
       </c>
       <c r="B76">
-        <v>22442156.96730407</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2">
+        <v>183795.0901244664</v>
+      </c>
+      <c r="C76">
+        <v>651175.142589791</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
       <c r="A77" s="2">
         <v>52504</v>
       </c>
       <c r="B77">
-        <v>19987354.57531404</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2">
+        <v>176218.5854736328</v>
+      </c>
+      <c r="C77">
+        <v>637036.2141127983</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
       <c r="A78" s="2">
         <v>52596</v>
       </c>
       <c r="B78">
-        <v>17801067.13901651</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2">
+        <v>168943.0870666171</v>
+      </c>
+      <c r="C78">
+        <v>623158.422262344</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
       <c r="A79" s="2">
         <v>52687</v>
       </c>
       <c r="B79">
-        <v>15644163.18854253</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2">
+        <v>160916.9781660318</v>
+      </c>
+      <c r="C79">
+        <v>609550.4614547375</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
       <c r="A80" s="2">
         <v>52778</v>
       </c>
       <c r="B80">
-        <v>13748605.0672372</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2">
+        <v>153261.7775633372</v>
+      </c>
+      <c r="C80">
+        <v>596234.6977678415</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
       <c r="A81" s="2">
         <v>52870</v>
       </c>
       <c r="B81">
-        <v>12082726.25495104</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2">
+        <v>145962.339584374</v>
+      </c>
+      <c r="C81">
+        <v>583200.4369277182</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
       <c r="A82" s="2">
         <v>52962</v>
       </c>
       <c r="B82">
-        <v>10618697.17240664</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2">
+        <v>139003.8336247177</v>
+      </c>
+      <c r="C82">
+        <v>570437.5736815296</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
       <c r="A83" s="2">
         <v>53052</v>
       </c>
       <c r="B83">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2">
+        <v>131439.0484698703</v>
+      </c>
+      <c r="C83">
+        <v>557944.7674798979</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
       <c r="A84" s="2">
         <v>53143</v>
       </c>
       <c r="B84">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2">
+        <v>124280.464177723</v>
+      </c>
+      <c r="C84">
+        <v>545727.7361964054</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
       <c r="A85" s="2">
         <v>53235</v>
       </c>
       <c r="B85">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2">
+        <v>117507.7240973007</v>
+      </c>
+      <c r="C85">
+        <v>533775.1242501298</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
       <c r="A86" s="2">
         <v>53327</v>
       </c>
       <c r="B86">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2">
+        <v>111101.2374976123</v>
+      </c>
+      <c r="C86">
+        <v>522076.2968077384</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
       <c r="A87" s="2">
         <v>53417</v>
       </c>
       <c r="B87">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2">
+        <v>103053.5182444882</v>
+      </c>
+      <c r="C87">
+        <v>510628.4875805905</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
       <c r="A88" s="2">
         <v>53508</v>
       </c>
       <c r="B88">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2">
+        <v>96774.54527766144</v>
+      </c>
+      <c r="C88">
+        <v>499436.1003577149</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
       <c r="A89" s="2">
         <v>53600</v>
       </c>
       <c r="B89">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2">
+        <v>90871.22740882236</v>
+      </c>
+      <c r="C89">
+        <v>488489.2492675122</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
       <c r="A90" s="2">
         <v>53692</v>
       </c>
       <c r="B90">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2">
+        <v>85322.66347896098</v>
+      </c>
+      <c r="C90">
+        <v>477778.6236000648</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
       <c r="A91" s="2">
         <v>53782</v>
       </c>
       <c r="B91">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2">
+        <v>79454.13139498538</v>
+      </c>
+      <c r="C91">
+        <v>467297.5034163803</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
       <c r="A92" s="2">
         <v>53873</v>
       </c>
       <c r="B92">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2">
+        <v>73985.57467466671</v>
+      </c>
+      <c r="C92">
+        <v>457041.1495947195</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
       <c r="A93" s="2">
         <v>53965</v>
       </c>
       <c r="B93">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2">
+        <v>68890.88446346263</v>
+      </c>
+      <c r="C93">
+        <v>447000.8377556725</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
       <c r="A94" s="2">
         <v>54057</v>
       </c>
       <c r="B94">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2">
+        <v>64145.4187113038</v>
+      </c>
+      <c r="C94">
+        <v>437168.4233276521</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
       <c r="A95" s="2">
         <v>54148</v>
       </c>
       <c r="B95">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2">
+        <v>59190.02389968468</v>
+      </c>
+      <c r="C95">
+        <v>427522.5120694301</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
       <c r="A96" s="2">
         <v>54239</v>
       </c>
       <c r="B96">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2">
+        <v>54617.05472362115</v>
+      </c>
+      <c r="C96">
+        <v>418029.0652782136</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
       <c r="A97" s="2">
         <v>54331</v>
       </c>
       <c r="B97">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2">
+        <v>50397.57428114624</v>
+      </c>
+      <c r="C97">
+        <v>408682.7691373453</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
       <c r="A98" s="2">
         <v>54423</v>
       </c>
       <c r="B98">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2">
+        <v>46504.68503611819</v>
+      </c>
+      <c r="C98">
+        <v>399478.9618416124</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
       <c r="A99" s="2">
         <v>54513</v>
       </c>
       <c r="B99">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2">
+        <v>42486.50727835399</v>
+      </c>
+      <c r="C99">
+        <v>390430.0476329227</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
       <c r="A100" s="2">
         <v>54604</v>
       </c>
       <c r="B100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2">
+        <v>38816.83925445018</v>
+      </c>
+      <c r="C100">
+        <v>381563.5902691117</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
       <c r="A101" s="2">
         <v>54696</v>
       </c>
       <c r="B101">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2">
+        <v>35465.63732654837</v>
+      </c>
+      <c r="C101">
+        <v>372873.419900983</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
       <c r="A102" s="2">
         <v>54788</v>
       </c>
       <c r="B102">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2">
+        <v>32405.3671417427</v>
+      </c>
+      <c r="C102">
+        <v>364354.0668574232</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
       <c r="A103" s="2">
         <v>54878</v>
       </c>
       <c r="B103">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2">
+        <v>29286.03466320341</v>
+      </c>
+      <c r="C103">
+        <v>355938.3101909123</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
       <c r="A104" s="2">
         <v>54969</v>
       </c>
       <c r="B104">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2">
+        <v>26468.87635332792</v>
+      </c>
+      <c r="C104">
+        <v>347621.9083978062</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
       <c r="A105" s="2">
         <v>55061</v>
       </c>
       <c r="B105">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2">
+        <v>23924.57705243365</v>
+      </c>
+      <c r="C105">
+        <v>339614.4065109796</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
       <c r="A106" s="2">
         <v>55153</v>
       </c>
       <c r="B106">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2">
+        <v>21626.63429545731</v>
+      </c>
+      <c r="C106">
+        <v>331865.0556563404</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
       <c r="A107" s="2">
         <v>55243</v>
       </c>
       <c r="B107">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2">
+        <v>17220.18443524502</v>
+      </c>
+      <c r="C107">
+        <v>324183.6302945121</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
       <c r="A108" s="2">
         <v>55334</v>
       </c>
       <c r="B108">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2">
+        <v>15434.94672805349</v>
+      </c>
+      <c r="C108">
+        <v>316501.0237407932</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
       <c r="A109" s="2">
         <v>55426</v>
       </c>
       <c r="B109">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2">
+        <v>13835.33024238186</v>
+      </c>
+      <c r="C109">
+        <v>309133.9919202846</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
       <c r="A110" s="2">
         <v>55518</v>
       </c>
       <c r="B110">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2">
+        <v>12401.97713763505</v>
+      </c>
+      <c r="C110">
+        <v>302011.8084599866</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
       <c r="A111" s="2">
         <v>55609</v>
       </c>
       <c r="B111">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2">
+        <v>10976.37103643571</v>
+      </c>
+      <c r="C111">
+        <v>295038.4985510078</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
       <c r="A112" s="2">
         <v>55700</v>
       </c>
       <c r="B112">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2">
+        <v>9715.071126467328</v>
+      </c>
+      <c r="C112">
+        <v>288197.0991409786</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
       <c r="A113" s="2">
         <v>55792</v>
       </c>
       <c r="B113">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2">
+        <v>8599.089472021702</v>
+      </c>
+      <c r="C113">
+        <v>281484.1664686711</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
       <c r="A114" s="2">
         <v>55884</v>
       </c>
       <c r="B114">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2">
+        <v>7611.638472260149</v>
+      </c>
+      <c r="C114">
+        <v>274896.5159832385</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
       <c r="A115" s="2">
         <v>55974</v>
       </c>
       <c r="B115">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2">
+        <v>4325.140607579247</v>
+      </c>
+      <c r="C115">
+        <v>268437.0988246495</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
       <c r="A116" s="2">
         <v>56065</v>
       </c>
       <c r="B116">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2">
+        <v>3796.274867197232</v>
+      </c>
+      <c r="C116">
+        <v>262114.3321981549</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
       <c r="A117" s="2">
         <v>56157</v>
       </c>
       <c r="B117">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2">
+        <v>3332.077306818355</v>
+      </c>
+      <c r="C117">
+        <v>255924.5275148532</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
       <c r="A118" s="2">
         <v>56249</v>
       </c>
       <c r="B118">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2">
+        <v>2924.640487586967</v>
+      </c>
+      <c r="C118">
+        <v>249864.2714558918</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
       <c r="A119" s="2">
         <v>56339</v>
       </c>
       <c r="B119">
         <v>0</v>
       </c>
-    </row>
-    <row r="120" spans="1:2">
+      <c r="C119">
+        <v>243900.5374199245</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
       <c r="A120" s="2">
         <v>56430</v>
       </c>
       <c r="B120">
         <v>0</v>
       </c>
-    </row>
-    <row r="121" spans="1:2">
+      <c r="C120">
+        <v>238023.8098826356</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
       <c r="A121" s="2">
         <v>56522</v>
       </c>
       <c r="B121">
         <v>0</v>
       </c>
-    </row>
-    <row r="122" spans="1:2">
+      <c r="C121">
+        <v>232320.405776653</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3">
       <c r="A122" s="2">
         <v>56614</v>
       </c>
       <c r="B122">
         <v>0</v>
       </c>
-    </row>
-    <row r="123" spans="1:2">
+      <c r="C122">
+        <v>226768.1490006755</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
       <c r="A123" s="2">
         <v>56704</v>
       </c>
       <c r="B123">
         <v>0</v>
       </c>
-    </row>
-    <row r="124" spans="1:2">
+      <c r="C123">
+        <v>221342.1387856178</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3">
       <c r="A124" s="2">
         <v>56795</v>
       </c>
       <c r="B124">
         <v>0</v>
       </c>
-    </row>
-    <row r="125" spans="1:2">
+      <c r="C124">
+        <v>216043.0405056324</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3">
       <c r="A125" s="2">
         <v>56887</v>
       </c>
       <c r="B125">
         <v>0</v>
       </c>
-    </row>
-    <row r="126" spans="1:2">
+      <c r="C125">
+        <v>210867.3991506137</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3">
       <c r="A126" s="2">
         <v>56979</v>
       </c>
       <c r="B126">
         <v>0</v>
       </c>
-    </row>
-    <row r="127" spans="1:2">
+      <c r="C126">
+        <v>205811.9061876057</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3">
       <c r="A127" s="2">
         <v>57070</v>
       </c>
       <c r="B127">
         <v>0</v>
       </c>
-    </row>
-    <row r="128" spans="1:2">
+      <c r="C127">
+        <v>200875.9087091269</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3">
       <c r="A128" s="2">
         <v>57161</v>
       </c>
       <c r="B128">
         <v>0</v>
       </c>
-    </row>
-    <row r="129" spans="1:2">
+      <c r="C128">
+        <v>196061.1270648089</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3">
       <c r="A129" s="2">
         <v>57253</v>
       </c>
       <c r="B129">
         <v>0</v>
       </c>
-    </row>
-    <row r="130" spans="1:2">
+      <c r="C129">
+        <v>191364.1418978194</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3">
       <c r="A130" s="2">
         <v>57345</v>
       </c>
       <c r="B130">
         <v>0</v>
       </c>
-    </row>
-    <row r="131" spans="1:2">
+      <c r="C130">
+        <v>186781.6624986</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3">
       <c r="A131" s="2">
         <v>57435</v>
       </c>
       <c r="B131">
         <v>0</v>
       </c>
-    </row>
-    <row r="132" spans="1:2">
+      <c r="C131">
+        <v>182312.5947588936</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3">
       <c r="A132" s="2">
         <v>57526</v>
       </c>
       <c r="B132">
         <v>0</v>
       </c>
-    </row>
-    <row r="133" spans="1:2">
+      <c r="C132">
+        <v>177957.80540352</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3">
       <c r="A133" s="2">
         <v>57618</v>
       </c>
       <c r="B133">
         <v>0</v>
       </c>
-    </row>
-    <row r="134" spans="1:2">
+      <c r="C133">
+        <v>173713.951053932</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3">
       <c r="A134" s="2">
         <v>57710</v>
       </c>
       <c r="B134">
         <v>0</v>
       </c>
-    </row>
-    <row r="135" spans="1:2">
+      <c r="C134">
+        <v>169577.8103950986</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3">
       <c r="A135" s="2">
         <v>57800</v>
       </c>
       <c r="B135">
         <v>0</v>
       </c>
-    </row>
-    <row r="136" spans="1:2">
+      <c r="C135">
+        <v>165570.7139290041</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3">
       <c r="A136" s="2">
         <v>57891</v>
       </c>
       <c r="B136">
         <v>0</v>
       </c>
-    </row>
-    <row r="137" spans="1:2">
+      <c r="C136">
+        <v>161735.6604762602</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3">
       <c r="A137" s="2">
         <v>57983</v>
       </c>
       <c r="B137">
         <v>0</v>
       </c>
-    </row>
-    <row r="138" spans="1:2">
+      <c r="C137">
+        <v>158066.2680797382</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3">
       <c r="A138" s="2">
         <v>58075</v>
       </c>
       <c r="B138">
         <v>0</v>
       </c>
-    </row>
-    <row r="139" spans="1:2">
+      <c r="C138">
+        <v>154558.6504101938</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3">
       <c r="A139" s="2">
         <v>58165</v>
       </c>
       <c r="B139">
         <v>0</v>
       </c>
-    </row>
-    <row r="140" spans="1:2">
+      <c r="C139">
+        <v>149748.9706275448</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3">
       <c r="A140" s="2">
         <v>58256</v>
       </c>
       <c r="B140">
         <v>0</v>
       </c>
-    </row>
-    <row r="141" spans="1:2">
+      <c r="C140">
+        <v>143099.4342824741</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3">
       <c r="A141" s="2">
         <v>58348</v>
       </c>
       <c r="B141">
         <v>0</v>
       </c>
-    </row>
-    <row r="142" spans="1:2">
+      <c r="C141">
+        <v>138684.9379471696</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3">
       <c r="A142" s="2">
         <v>58440</v>
       </c>
       <c r="B142">
         <v>0</v>
       </c>
-    </row>
-    <row r="143" spans="1:2">
+      <c r="C142">
+        <v>135670.6872333313</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3">
       <c r="A143" s="2">
         <v>58531</v>
       </c>
       <c r="B143">
         <v>0</v>
       </c>
-    </row>
-    <row r="144" spans="1:2">
+      <c r="C143">
+        <v>130902.3030213865</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3">
       <c r="A144" s="2">
         <v>58622</v>
       </c>
       <c r="B144">
         <v>0</v>
       </c>
-    </row>
-    <row r="145" spans="1:2">
+      <c r="C144">
+        <v>123514.2551518584</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3">
       <c r="A145" s="2">
         <v>58714</v>
       </c>
       <c r="B145">
         <v>0</v>
       </c>
-    </row>
-    <row r="146" spans="1:2">
+      <c r="C145">
+        <v>119096.9655584228</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3">
       <c r="A146" s="2">
         <v>58806</v>
       </c>
       <c r="B146">
         <v>0</v>
       </c>
-    </row>
-    <row r="147" spans="1:2">
+      <c r="C146">
+        <v>116504.8784257245</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3">
       <c r="A147" s="2">
         <v>58896</v>
       </c>
       <c r="B147">
         <v>0</v>
       </c>
-    </row>
-    <row r="148" spans="1:2">
+      <c r="C147">
+        <v>112484.5898534138</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3">
       <c r="A148" s="2">
         <v>58987</v>
       </c>
       <c r="B148">
         <v>0</v>
       </c>
-    </row>
-    <row r="149" spans="1:2">
+      <c r="C148">
+        <v>106265.0343269653</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3">
       <c r="A149" s="2">
         <v>59079</v>
       </c>
       <c r="B149">
         <v>0</v>
       </c>
-    </row>
-    <row r="150" spans="1:2">
+      <c r="C149">
+        <v>102478.7781352302</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3">
       <c r="A150" s="2">
         <v>59171</v>
       </c>
       <c r="B150">
         <v>0</v>
       </c>
-    </row>
-    <row r="151" spans="1:2">
+      <c r="C150">
+        <v>100146.8874722679</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3">
       <c r="A151" s="2">
         <v>59261</v>
       </c>
       <c r="B151">
         <v>0</v>
       </c>
-    </row>
-    <row r="152" spans="1:2">
+      <c r="C151">
+        <v>97984.7972794191</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3">
       <c r="A152" s="2">
         <v>59352</v>
       </c>
       <c r="B152">
         <v>0</v>
       </c>
-    </row>
-    <row r="153" spans="1:2">
+      <c r="C152">
+        <v>95879.32462697357</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3">
       <c r="A153" s="2">
         <v>59444</v>
       </c>
       <c r="B153">
         <v>0</v>
       </c>
-    </row>
-    <row r="154" spans="1:2">
+      <c r="C153">
+        <v>93828.46456869166</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3">
       <c r="A154" s="2">
         <v>59536</v>
       </c>
       <c r="B154">
         <v>0</v>
       </c>
-    </row>
-    <row r="155" spans="1:2">
+      <c r="C154">
+        <v>91830.66071673777</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3">
       <c r="A155" s="2">
         <v>59626</v>
       </c>
       <c r="B155">
         <v>0</v>
       </c>
-    </row>
-    <row r="156" spans="1:2">
+      <c r="C155">
+        <v>89884.91432990026</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3">
       <c r="A156" s="2">
         <v>59717</v>
       </c>
       <c r="B156">
         <v>0</v>
       </c>
-    </row>
-    <row r="157" spans="1:2">
+      <c r="C156">
+        <v>87990.73001577597</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3">
       <c r="A157" s="2">
         <v>59809</v>
       </c>
       <c r="B157">
         <v>0</v>
       </c>
-    </row>
-    <row r="158" spans="1:2">
+      <c r="C157">
+        <v>86146.59547590453</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3">
       <c r="A158" s="2">
         <v>59901</v>
       </c>
       <c r="B158">
         <v>0</v>
       </c>
-    </row>
-    <row r="159" spans="1:2">
+      <c r="C158">
+        <v>84351.04579456386</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3">
       <c r="A159" s="2">
         <v>59992</v>
       </c>
       <c r="B159">
         <v>0</v>
       </c>
-    </row>
-    <row r="160" spans="1:2">
+      <c r="C159">
+        <v>82605.96375276303</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3">
       <c r="A160" s="2">
         <v>60083</v>
       </c>
       <c r="B160">
         <v>0</v>
       </c>
-    </row>
-    <row r="161" spans="1:2">
+      <c r="C160">
+        <v>80916.23053378325</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3">
       <c r="A161" s="2">
         <v>60175</v>
       </c>
       <c r="B161">
         <v>0</v>
       </c>
-    </row>
-    <row r="162" spans="1:2">
+      <c r="C161">
+        <v>79280.05606519966</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3">
       <c r="A162" s="2">
         <v>60267</v>
       </c>
       <c r="B162">
         <v>0</v>
       </c>
-    </row>
-    <row r="163" spans="1:2">
+      <c r="C162">
+        <v>77695.93044679888</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3">
       <c r="A163" s="2">
         <v>60357</v>
       </c>
       <c r="B163">
         <v>0</v>
       </c>
-    </row>
-    <row r="164" spans="1:2">
+      <c r="C163">
+        <v>75918.53994332376</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3">
       <c r="A164" s="2">
         <v>60448</v>
       </c>
       <c r="B164">
         <v>0</v>
       </c>
-    </row>
-    <row r="165" spans="1:2">
+      <c r="C164">
+        <v>73856.51545465084</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3">
       <c r="A165" s="2">
         <v>60540</v>
       </c>
       <c r="B165">
         <v>0</v>
       </c>
-    </row>
-    <row r="166" spans="1:2">
+      <c r="C165">
+        <v>72176.68823836165</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3">
       <c r="A166" s="2">
         <v>60632</v>
       </c>
       <c r="B166">
         <v>0</v>
       </c>
-    </row>
-    <row r="167" spans="1:2">
+      <c r="C166">
+        <v>70737.48525510285</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3">
       <c r="A167" s="2">
         <v>60722</v>
       </c>
       <c r="B167">
         <v>0</v>
       </c>
-    </row>
-    <row r="168" spans="1:2">
+      <c r="C167">
+        <v>69352.93626235539</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3">
       <c r="A168" s="2">
         <v>60813</v>
       </c>
       <c r="B168">
         <v>0</v>
       </c>
-    </row>
-    <row r="169" spans="1:2">
+      <c r="C168">
+        <v>68006.11504162816</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3">
       <c r="A169" s="2">
         <v>60905</v>
       </c>
       <c r="B169">
         <v>0</v>
       </c>
-    </row>
-    <row r="170" spans="1:2">
+      <c r="C169">
+        <v>66695.82585119075</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3">
       <c r="A170" s="2">
         <v>60997</v>
       </c>
       <c r="B170">
         <v>0</v>
       </c>
-    </row>
-    <row r="171" spans="1:2">
+      <c r="C170">
+        <v>65420.96870046581</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3">
       <c r="A171" s="2">
         <v>61087</v>
       </c>
       <c r="B171">
         <v>0</v>
       </c>
-    </row>
-    <row r="172" spans="1:2">
+      <c r="C171">
+        <v>64180.6919379327</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3">
       <c r="A172" s="2">
         <v>61178</v>
       </c>
       <c r="B172">
         <v>0</v>
       </c>
-    </row>
-    <row r="173" spans="1:2">
+      <c r="C172">
+        <v>62974.3712270727</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3">
       <c r="A173" s="2">
         <v>61270</v>
       </c>
       <c r="B173">
         <v>0</v>
       </c>
-    </row>
-    <row r="174" spans="1:2">
+      <c r="C173">
+        <v>61800.97834276476</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3">
       <c r="A174" s="2">
         <v>61362</v>
       </c>
       <c r="B174">
         <v>0</v>
       </c>
-    </row>
-    <row r="175" spans="1:2">
+      <c r="C174">
+        <v>60659.51981437137</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3">
       <c r="A175" s="2">
         <v>61453</v>
       </c>
       <c r="B175">
         <v>0</v>
       </c>
-    </row>
-    <row r="176" spans="1:2">
+      <c r="C175">
+        <v>59549.21987062716</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3">
       <c r="A176" s="2">
         <v>61544</v>
       </c>
       <c r="B176">
         <v>0</v>
       </c>
-    </row>
-    <row r="177" spans="1:2">
+      <c r="C176">
+        <v>58469.50261451749</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3">
       <c r="A177" s="2">
         <v>61636</v>
       </c>
       <c r="B177">
         <v>0</v>
       </c>
-    </row>
-    <row r="178" spans="1:2">
+      <c r="C177">
+        <v>57419.44275562591</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3">
       <c r="A178" s="2">
         <v>61728</v>
       </c>
       <c r="B178">
         <v>0</v>
       </c>
-    </row>
-    <row r="179" spans="1:2">
+      <c r="C178">
+        <v>56398.14664977409</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3">
       <c r="A179" s="2">
         <v>61818</v>
       </c>
       <c r="B179">
         <v>0</v>
       </c>
-    </row>
-    <row r="180" spans="1:2">
+      <c r="C179">
+        <v>55418.63008069097</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3">
       <c r="A180" s="2">
         <v>61909</v>
       </c>
       <c r="B180">
         <v>0</v>
       </c>
-    </row>
-    <row r="181" spans="1:2">
+      <c r="C180">
+        <v>54506.81614389252</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3">
       <c r="A181" s="2">
         <v>62001</v>
       </c>
       <c r="B181">
         <v>0</v>
       </c>
-    </row>
-    <row r="182" spans="1:2">
+      <c r="C181">
+        <v>53660.70549382266</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3">
       <c r="A182" s="2">
         <v>62093</v>
       </c>
       <c r="B182">
         <v>0</v>
       </c>
-    </row>
-    <row r="183" spans="1:2">
+      <c r="C182">
+        <v>52879.20824105258</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3">
       <c r="A183" s="2">
         <v>62183</v>
       </c>
       <c r="B183">
         <v>0</v>
       </c>
-    </row>
-    <row r="184" spans="1:2">
+      <c r="C183">
+        <v>50708.02246286332</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3">
       <c r="A184" s="2">
         <v>62274</v>
       </c>
       <c r="B184">
         <v>0</v>
       </c>
-    </row>
-    <row r="185" spans="1:2">
+      <c r="C184">
+        <v>46607.02462677911</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3">
       <c r="A185" s="2">
         <v>62366</v>
       </c>
       <c r="B185">
         <v>0</v>
       </c>
-    </row>
-    <row r="186" spans="1:2">
+      <c r="C185">
+        <v>44562.7711071612</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3">
       <c r="A186" s="2">
         <v>62458</v>
       </c>
       <c r="B186">
         <v>0</v>
       </c>
-    </row>
-    <row r="187" spans="1:2">
+      <c r="C186">
+        <v>43741.44594587414</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3">
       <c r="A187" s="2">
         <v>62548</v>
       </c>
       <c r="B187">
         <v>0</v>
       </c>
-    </row>
-    <row r="188" spans="1:2">
+      <c r="C187">
+        <v>43074.48327911768</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3">
       <c r="A188" s="2">
         <v>62639</v>
       </c>
       <c r="B188">
         <v>0</v>
       </c>
-    </row>
-    <row r="189" spans="1:2">
+      <c r="C188">
+        <v>42534.99494700089</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3">
       <c r="A189" s="2">
         <v>62731</v>
       </c>
       <c r="B189">
         <v>0</v>
       </c>
-    </row>
-    <row r="190" spans="1:2">
+      <c r="C189">
+        <v>42119.24534879037</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3">
       <c r="A190" s="2">
         <v>62823</v>
       </c>
       <c r="B190">
         <v>0</v>
       </c>
-    </row>
-    <row r="191" spans="1:2">
+      <c r="C190">
+        <v>41826.02349805112</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3">
       <c r="A191" s="2">
         <v>62914</v>
       </c>
       <c r="B191">
         <v>0</v>
       </c>
-    </row>
-    <row r="192" spans="1:2">
+      <c r="C191">
+        <v>37482.70916879612</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3">
       <c r="A192" s="2">
         <v>63005</v>
       </c>
       <c r="B192">
         <v>0</v>
       </c>
-    </row>
-    <row r="193" spans="1:2">
+      <c r="C192">
+        <v>27625.29355733244</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3">
       <c r="A193" s="2">
         <v>63097</v>
       </c>
       <c r="B193">
         <v>0</v>
       </c>
-    </row>
-    <row r="194" spans="1:2">
+      <c r="C193">
+        <v>23826.83181248081</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3">
       <c r="A194" s="2">
         <v>63189</v>
       </c>
       <c r="B194">
         <v>0</v>
       </c>
-    </row>
-    <row r="195" spans="1:2">
+      <c r="C194">
+        <v>23661.69672886991</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3">
       <c r="A195" s="2">
         <v>63279</v>
       </c>
       <c r="B195">
         <v>0</v>
       </c>
-    </row>
-    <row r="196" spans="1:2">
+      <c r="C195">
+        <v>18308.13582776803</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3">
       <c r="A196" s="2">
         <v>63370</v>
       </c>
       <c r="B196">
         <v>0</v>
       </c>
-    </row>
-    <row r="197" spans="1:2">
+      <c r="C196">
+        <v>5409.00512783337</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3">
       <c r="A197" s="2">
         <v>63462</v>
       </c>
       <c r="B197">
         <v>0</v>
       </c>
-    </row>
-    <row r="198" spans="1:2">
+      <c r="C197">
+        <v>380.4883555096199</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3">
       <c r="A198" s="2">
         <v>63554</v>
       </c>
       <c r="B198">
         <v>0</v>
       </c>
-    </row>
-    <row r="199" spans="1:2">
+      <c r="C198">
+        <v>1.338244143395779</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3">
       <c r="A199" s="2">
         <v>63644</v>
       </c>
       <c r="B199">
         <v>0</v>
       </c>
-    </row>
-    <row r="200" spans="1:2">
+      <c r="C199">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3">
       <c r="A200" s="2">
         <v>63735</v>
       </c>
       <c r="B200">
         <v>0</v>
       </c>
-    </row>
-    <row r="201" spans="1:2">
+      <c r="C200">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3">
       <c r="A201" s="2">
         <v>63827</v>
       </c>
       <c r="B201">
         <v>0</v>
       </c>
-    </row>
-    <row r="202" spans="1:2">
+      <c r="C201">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3">
       <c r="A202" s="2">
         <v>63919</v>
       </c>
       <c r="B202">
+        <v>0</v>
+      </c>
+      <c r="C202">
         <v>0</v>
       </c>
     </row>
